--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D5DA01-5644-4FA4-8F72-4B170742A093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEF3A7E-2907-40B5-84F3-32979BB56B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11305" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11478" uniqueCount="602">
   <si>
     <t>Semana</t>
   </si>
@@ -1816,6 +1816,39 @@
   <si>
     <t>Curl de isquios en maquina unilateral</t>
   </si>
+  <si>
+    <t>2x8 (65% RM) 2x6 (75% RM)</t>
+  </si>
+  <si>
+    <t>Bench Press inclinado con mancuernas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable crossover </t>
+  </si>
+  <si>
+    <t>7 cada lado</t>
+  </si>
+  <si>
+    <t>3x6 (75% RM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3x10 cada brazo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4x12 </t>
+  </si>
+  <si>
+    <t>(Bonus) Curl barra W</t>
+  </si>
+  <si>
+    <t>Curl con mancuernas</t>
+  </si>
+  <si>
+    <t>Press frances unilat en polea</t>
+  </si>
+  <si>
+    <t>15'' cada lado</t>
+  </si>
 </sst>
 </file>
 
@@ -2208,7 +2241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2303,6 +2336,7 @@
     <xf numFmtId="0" fontId="2" fillId="52" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="54" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -72301,7 +72335,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:L313"/>
+  <dimension ref="A1:L360"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -80387,9 +80421,1202 @@
       </c>
       <c r="I313" s="63"/>
     </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="24">
+        <v>8</v>
+      </c>
+      <c r="B314" s="8">
+        <v>1</v>
+      </c>
+      <c r="C314" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D314" s="8">
+        <v>1</v>
+      </c>
+      <c r="E314" s="8">
+        <v>2</v>
+      </c>
+      <c r="F314" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G314" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H314" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I314" s="92"/>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="24">
+        <v>8</v>
+      </c>
+      <c r="B315" s="8">
+        <v>1</v>
+      </c>
+      <c r="C315" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D315" s="8">
+        <v>1</v>
+      </c>
+      <c r="E315" s="8">
+        <v>2</v>
+      </c>
+      <c r="F315" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G315" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H315" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I315" s="92"/>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="24">
+        <v>8</v>
+      </c>
+      <c r="B316" s="8">
+        <v>1</v>
+      </c>
+      <c r="C316" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D316" s="8">
+        <v>1</v>
+      </c>
+      <c r="E316" s="8">
+        <v>2</v>
+      </c>
+      <c r="F316" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G316" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H316" s="8">
+        <v>10</v>
+      </c>
+      <c r="I316" s="92"/>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="24">
+        <v>8</v>
+      </c>
+      <c r="B317" s="8">
+        <v>1</v>
+      </c>
+      <c r="C317" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D317" s="8">
+        <v>1</v>
+      </c>
+      <c r="E317" s="8">
+        <v>2</v>
+      </c>
+      <c r="F317" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G317" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H317" s="8">
+        <v>8</v>
+      </c>
+      <c r="I317" s="92"/>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="24">
+        <v>8</v>
+      </c>
+      <c r="B318" s="8">
+        <v>1</v>
+      </c>
+      <c r="C318" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D318" s="8">
+        <v>1</v>
+      </c>
+      <c r="E318" s="8">
+        <v>2</v>
+      </c>
+      <c r="F318" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G318" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H318" s="8">
+        <v>8</v>
+      </c>
+      <c r="I318" s="92"/>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="24">
+        <v>8</v>
+      </c>
+      <c r="B319" s="8">
+        <v>1</v>
+      </c>
+      <c r="C319" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D319" s="8">
+        <v>1</v>
+      </c>
+      <c r="E319" s="8">
+        <v>2</v>
+      </c>
+      <c r="F319" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G319" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H319" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I319" s="92"/>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="24">
+        <v>8</v>
+      </c>
+      <c r="B320" s="24">
+        <v>1</v>
+      </c>
+      <c r="C320" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D320" s="23"/>
+      <c r="E320" s="23"/>
+      <c r="F320" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G320" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H320" s="23" t="s">
+        <v>591</v>
+      </c>
+      <c r="I320" s="92"/>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="24">
+        <v>8</v>
+      </c>
+      <c r="B321" s="24">
+        <v>1</v>
+      </c>
+      <c r="C321" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D321" s="23"/>
+      <c r="E321" s="23"/>
+      <c r="F321" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="G321" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H321" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="I321" s="92"/>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="24">
+        <v>8</v>
+      </c>
+      <c r="B322" s="24">
+        <v>1</v>
+      </c>
+      <c r="C322" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D322" s="23"/>
+      <c r="E322" s="23"/>
+      <c r="F322" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="G322" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H322" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="I322" s="92"/>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" s="24">
+        <v>8</v>
+      </c>
+      <c r="B323" s="24">
+        <v>1</v>
+      </c>
+      <c r="C323" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D323" s="23"/>
+      <c r="E323" s="23"/>
+      <c r="F323" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="G323" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H323" s="23" t="s">
+        <v>591</v>
+      </c>
+      <c r="I323" s="92"/>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="24">
+        <v>8</v>
+      </c>
+      <c r="B324" s="24">
+        <v>1</v>
+      </c>
+      <c r="C324" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D324" s="23"/>
+      <c r="E324" s="23"/>
+      <c r="F324" s="23" t="s">
+        <v>593</v>
+      </c>
+      <c r="G324" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H324" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="I324" s="92"/>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" s="24">
+        <v>8</v>
+      </c>
+      <c r="B325" s="24">
+        <v>1</v>
+      </c>
+      <c r="C325" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D325" s="23"/>
+      <c r="E325" s="23"/>
+      <c r="F325" s="23" t="s">
+        <v>592</v>
+      </c>
+      <c r="G325" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H325" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="I325" s="92"/>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" s="24">
+        <v>8</v>
+      </c>
+      <c r="B326" s="24">
+        <v>1</v>
+      </c>
+      <c r="C326" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D326" s="23"/>
+      <c r="E326" s="23"/>
+      <c r="F326" s="23" t="s">
+        <v>559</v>
+      </c>
+      <c r="G326" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H326" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="I326" s="92"/>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" s="24">
+        <v>8</v>
+      </c>
+      <c r="B327" s="24">
+        <v>1</v>
+      </c>
+      <c r="C327" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D327" s="23">
+        <v>2</v>
+      </c>
+      <c r="E327" s="23">
+        <v>3</v>
+      </c>
+      <c r="F327" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="G327" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H327" s="23">
+        <v>20</v>
+      </c>
+      <c r="I327" s="92"/>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" s="24">
+        <v>8</v>
+      </c>
+      <c r="B328" s="24">
+        <v>1</v>
+      </c>
+      <c r="C328" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D328" s="23">
+        <v>2</v>
+      </c>
+      <c r="E328" s="23">
+        <v>3</v>
+      </c>
+      <c r="F328" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="G328" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H328" s="23">
+        <v>20</v>
+      </c>
+      <c r="I328" s="92"/>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" s="24">
+        <v>8</v>
+      </c>
+      <c r="B329" s="24">
+        <v>1</v>
+      </c>
+      <c r="C329" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D329" s="23">
+        <v>2</v>
+      </c>
+      <c r="E329" s="23">
+        <v>3</v>
+      </c>
+      <c r="F329" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="G329" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H329" s="23" t="s">
+        <v>594</v>
+      </c>
+      <c r="I329" s="92"/>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" s="24">
+        <v>8</v>
+      </c>
+      <c r="B330" s="10">
+        <v>2</v>
+      </c>
+      <c r="C330" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D330" s="11">
+        <v>1</v>
+      </c>
+      <c r="E330" s="11">
+        <v>2</v>
+      </c>
+      <c r="F330" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G330" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H330" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I330" s="92"/>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" s="24">
+        <v>8</v>
+      </c>
+      <c r="B331" s="10">
+        <v>2</v>
+      </c>
+      <c r="C331" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D331" s="11">
+        <v>1</v>
+      </c>
+      <c r="E331" s="11">
+        <v>2</v>
+      </c>
+      <c r="F331" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G331" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H331" s="10">
+        <v>10</v>
+      </c>
+      <c r="I331" s="92"/>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="24">
+        <v>8</v>
+      </c>
+      <c r="B332" s="10">
+        <v>2</v>
+      </c>
+      <c r="C332" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D332" s="11">
+        <v>1</v>
+      </c>
+      <c r="E332" s="11">
+        <v>2</v>
+      </c>
+      <c r="F332" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G332" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H332" s="10">
+        <v>10</v>
+      </c>
+      <c r="I332" s="92"/>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" s="24">
+        <v>8</v>
+      </c>
+      <c r="B333" s="10">
+        <v>2</v>
+      </c>
+      <c r="C333" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D333" s="11">
+        <v>1</v>
+      </c>
+      <c r="E333" s="11">
+        <v>2</v>
+      </c>
+      <c r="F333" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G333" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H333" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I333" s="92"/>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="24">
+        <v>8</v>
+      </c>
+      <c r="B334" s="10">
+        <v>2</v>
+      </c>
+      <c r="C334" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D334" s="11">
+        <v>1</v>
+      </c>
+      <c r="E334" s="11">
+        <v>2</v>
+      </c>
+      <c r="F334" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G334" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H334" s="10">
+        <v>10</v>
+      </c>
+      <c r="I334" s="92"/>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="24">
+        <v>8</v>
+      </c>
+      <c r="B335" s="10">
+        <v>2</v>
+      </c>
+      <c r="C335" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D335" s="11">
+        <v>1</v>
+      </c>
+      <c r="E335" s="11">
+        <v>2</v>
+      </c>
+      <c r="F335" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G335" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H335" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I335" s="92"/>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="24">
+        <v>8</v>
+      </c>
+      <c r="B336" s="23">
+        <v>2</v>
+      </c>
+      <c r="C336" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D336" s="23"/>
+      <c r="E336" s="23"/>
+      <c r="F336" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G336" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H336" s="23" t="s">
+        <v>591</v>
+      </c>
+      <c r="I336" s="92"/>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="24">
+        <v>8</v>
+      </c>
+      <c r="B337" s="23">
+        <v>2</v>
+      </c>
+      <c r="C337" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D337" s="23"/>
+      <c r="E337" s="23"/>
+      <c r="F337" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G337" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H337" s="23" t="s">
+        <v>595</v>
+      </c>
+      <c r="I337" s="92"/>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="24">
+        <v>8</v>
+      </c>
+      <c r="B338" s="23">
+        <v>2</v>
+      </c>
+      <c r="C338" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D338" s="23"/>
+      <c r="E338" s="23"/>
+      <c r="F338" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="G338" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H338" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="I338" s="92"/>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="24">
+        <v>8</v>
+      </c>
+      <c r="B339" s="23">
+        <v>2</v>
+      </c>
+      <c r="C339" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D339" s="23"/>
+      <c r="E339" s="23"/>
+      <c r="F339" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="G339" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H339" s="23" t="s">
+        <v>591</v>
+      </c>
+      <c r="I339" s="92"/>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="24">
+        <v>8</v>
+      </c>
+      <c r="B340" s="23">
+        <v>2</v>
+      </c>
+      <c r="C340" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D340" s="23"/>
+      <c r="E340" s="23"/>
+      <c r="F340" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="G340" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H340" s="23" t="s">
+        <v>596</v>
+      </c>
+      <c r="I340" s="92"/>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="24">
+        <v>8</v>
+      </c>
+      <c r="B341" s="23">
+        <v>2</v>
+      </c>
+      <c r="C341" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D341" s="23"/>
+      <c r="E341" s="23"/>
+      <c r="F341" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="G341" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H341" s="23" t="s">
+        <v>597</v>
+      </c>
+      <c r="I341" s="92"/>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="24">
+        <v>8</v>
+      </c>
+      <c r="B342" s="23">
+        <v>2</v>
+      </c>
+      <c r="C342" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D342" s="23"/>
+      <c r="E342" s="23"/>
+      <c r="F342" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="G342" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H342" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="I342" s="92"/>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" s="24">
+        <v>8</v>
+      </c>
+      <c r="B343" s="23">
+        <v>2</v>
+      </c>
+      <c r="C343" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D343" s="23"/>
+      <c r="E343" s="23"/>
+      <c r="F343" s="23" t="s">
+        <v>598</v>
+      </c>
+      <c r="G343" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H343" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="I343" s="92"/>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" s="24">
+        <v>8</v>
+      </c>
+      <c r="B344" s="23">
+        <v>2</v>
+      </c>
+      <c r="C344" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D344" s="23">
+        <v>2</v>
+      </c>
+      <c r="E344" s="23">
+        <v>3</v>
+      </c>
+      <c r="F344" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="G344" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H344" s="23">
+        <v>20</v>
+      </c>
+      <c r="I344" s="92"/>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" s="24">
+        <v>8</v>
+      </c>
+      <c r="B345" s="23">
+        <v>2</v>
+      </c>
+      <c r="C345" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D345" s="23">
+        <v>2</v>
+      </c>
+      <c r="E345" s="23">
+        <v>3</v>
+      </c>
+      <c r="F345" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="G345" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H345" s="23">
+        <v>10</v>
+      </c>
+      <c r="I345" s="92"/>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" s="24">
+        <v>8</v>
+      </c>
+      <c r="B346" s="23">
+        <v>2</v>
+      </c>
+      <c r="C346" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D346" s="23">
+        <v>2</v>
+      </c>
+      <c r="E346" s="23">
+        <v>3</v>
+      </c>
+      <c r="F346" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="G346" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H346" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I346" s="92"/>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" s="24">
+        <v>8</v>
+      </c>
+      <c r="B347" s="12">
+        <v>3</v>
+      </c>
+      <c r="C347" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D347" s="13">
+        <v>1</v>
+      </c>
+      <c r="E347" s="13">
+        <v>2</v>
+      </c>
+      <c r="F347" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G347" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H347" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I347" s="92"/>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" s="24">
+        <v>8</v>
+      </c>
+      <c r="B348" s="12">
+        <v>3</v>
+      </c>
+      <c r="C348" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D348" s="13">
+        <v>1</v>
+      </c>
+      <c r="E348" s="13">
+        <v>2</v>
+      </c>
+      <c r="F348" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G348" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H348" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I348" s="92"/>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" s="24">
+        <v>8</v>
+      </c>
+      <c r="B349" s="12">
+        <v>3</v>
+      </c>
+      <c r="C349" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D349" s="13">
+        <v>1</v>
+      </c>
+      <c r="E349" s="13">
+        <v>2</v>
+      </c>
+      <c r="F349" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G349" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H349" s="12">
+        <v>7</v>
+      </c>
+      <c r="I349" s="92"/>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" s="24">
+        <v>8</v>
+      </c>
+      <c r="B350" s="12">
+        <v>3</v>
+      </c>
+      <c r="C350" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D350" s="13">
+        <v>1</v>
+      </c>
+      <c r="E350" s="13">
+        <v>2</v>
+      </c>
+      <c r="F350" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G350" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H350" s="12">
+        <v>8</v>
+      </c>
+      <c r="I350" s="92"/>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" s="24">
+        <v>8</v>
+      </c>
+      <c r="B351" s="12">
+        <v>3</v>
+      </c>
+      <c r="C351" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D351" s="13">
+        <v>1</v>
+      </c>
+      <c r="E351" s="13">
+        <v>2</v>
+      </c>
+      <c r="F351" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G351" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H351" s="12">
+        <v>8</v>
+      </c>
+      <c r="I351" s="92"/>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" s="24">
+        <v>8</v>
+      </c>
+      <c r="B352" s="12">
+        <v>3</v>
+      </c>
+      <c r="C352" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D352" s="13">
+        <v>1</v>
+      </c>
+      <c r="E352" s="13">
+        <v>2</v>
+      </c>
+      <c r="F352" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G352" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H352" s="12">
+        <v>10</v>
+      </c>
+      <c r="I352" s="92"/>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" s="24">
+        <v>8</v>
+      </c>
+      <c r="B353" s="23">
+        <v>3</v>
+      </c>
+      <c r="C353" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D353" s="23"/>
+      <c r="E353" s="23"/>
+      <c r="F353" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="G353" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H353" s="23" t="s">
+        <v>591</v>
+      </c>
+      <c r="I353" s="92"/>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" s="24">
+        <v>8</v>
+      </c>
+      <c r="B354" s="23">
+        <v>3</v>
+      </c>
+      <c r="C354" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D354" s="23"/>
+      <c r="E354" s="23"/>
+      <c r="F354" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="G354" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H354" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="I354" s="92"/>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" s="24">
+        <v>8</v>
+      </c>
+      <c r="B355" s="23">
+        <v>3</v>
+      </c>
+      <c r="C355" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D355" s="92"/>
+      <c r="E355" s="92"/>
+      <c r="F355" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="G355" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H355" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="I355" s="92"/>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" s="24">
+        <v>8</v>
+      </c>
+      <c r="B356" s="23">
+        <v>3</v>
+      </c>
+      <c r="C356" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D356" s="92"/>
+      <c r="E356" s="92"/>
+      <c r="F356" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="G356" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H356" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="I356" s="92"/>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" s="24">
+        <v>8</v>
+      </c>
+      <c r="B357" s="23">
+        <v>3</v>
+      </c>
+      <c r="C357" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D357" s="92">
+        <v>2</v>
+      </c>
+      <c r="E357" s="92">
+        <v>3</v>
+      </c>
+      <c r="F357" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G357" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H357" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="I357" s="92"/>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" s="24">
+        <v>8</v>
+      </c>
+      <c r="B358" s="23">
+        <v>3</v>
+      </c>
+      <c r="C358" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D358" s="92">
+        <v>2</v>
+      </c>
+      <c r="E358" s="92">
+        <v>3</v>
+      </c>
+      <c r="F358" s="23" t="s">
+        <v>599</v>
+      </c>
+      <c r="G358" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H358" s="92">
+        <v>10</v>
+      </c>
+      <c r="I358" s="92"/>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" s="24">
+        <v>8</v>
+      </c>
+      <c r="B359" s="23">
+        <v>3</v>
+      </c>
+      <c r="C359" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D359" s="92">
+        <v>3</v>
+      </c>
+      <c r="E359" s="92">
+        <v>3</v>
+      </c>
+      <c r="F359" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G359" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H359" s="23" t="s">
+        <v>601</v>
+      </c>
+      <c r="I359" s="92"/>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" s="24">
+        <v>8</v>
+      </c>
+      <c r="B360" s="23">
+        <v>3</v>
+      </c>
+      <c r="C360" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D360" s="92">
+        <v>3</v>
+      </c>
+      <c r="E360" s="92">
+        <v>3</v>
+      </c>
+      <c r="F360" s="23" t="s">
+        <v>600</v>
+      </c>
+      <c r="G360" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H360" s="92" t="s">
+        <v>99</v>
+      </c>
+      <c r="I360" s="92"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C313" xr:uid="{00000000-0002-0000-0700-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C360" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEF3A7E-2907-40B5-84F3-32979BB56B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78548284-F57A-4286-B9BB-8A32FB40A02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="1" r:id="rId1"/>
@@ -35,14 +35,15 @@
     <sheet name="Mara Tomanovich" sheetId="21" r:id="rId20"/>
     <sheet name="Leo Lewis" sheetId="22" r:id="rId21"/>
     <sheet name="Federico Suarez" sheetId="23" r:id="rId22"/>
-    <sheet name="Alumnos" sheetId="20" r:id="rId23"/>
+    <sheet name="Cristian Medina" sheetId="24" r:id="rId23"/>
+    <sheet name="Alumnos" sheetId="20" r:id="rId24"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11478" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12479" uniqueCount="614">
   <si>
     <t>Semana</t>
   </si>
@@ -1849,6 +1850,42 @@
   <si>
     <t>15'' cada lado</t>
   </si>
+  <si>
+    <t>9283</t>
+  </si>
+  <si>
+    <t>Cristian Medina</t>
+  </si>
+  <si>
+    <t>| Cristian Medina | 9283 |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x7 (60% RM) 2x5 (70%) 2x3 (85%) </t>
+  </si>
+  <si>
+    <t>1x8 2x6 2x4 (Aumentando la carga)</t>
+  </si>
+  <si>
+    <t>2x6 2x4 (Aumentando la carga)</t>
+  </si>
+  <si>
+    <t>1x7 4x5 (Aumentando la carga)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x7 3x5 (Aumentando la carga) </t>
+  </si>
+  <si>
+    <t>Pull down agarre neutro (triangulo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vuelos frontales   </t>
+  </si>
+  <si>
+    <t>Plank con peso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3x12 </t>
+  </si>
 </sst>
 </file>
 
@@ -2241,7 +2278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2337,6 +2374,7 @@
     <xf numFmtId="0" fontId="2" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="54" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2639,7 +2677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -2740,6 +2778,11 @@
         <v>565</v>
       </c>
     </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>604</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2747,7 +2790,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -7102,6 +7145,864 @@
       </c>
       <c r="H168" s="36">
         <v>30</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="46">
+        <v>6</v>
+      </c>
+      <c r="B169" s="46">
+        <v>1</v>
+      </c>
+      <c r="C169" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="46">
+        <v>1</v>
+      </c>
+      <c r="E169" s="46">
+        <v>2</v>
+      </c>
+      <c r="F169" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G169" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H169" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="46">
+        <v>6</v>
+      </c>
+      <c r="B170" s="46">
+        <v>1</v>
+      </c>
+      <c r="C170" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" s="46">
+        <v>1</v>
+      </c>
+      <c r="E170" s="46">
+        <v>2</v>
+      </c>
+      <c r="F170" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G170" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H170" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="46">
+        <v>6</v>
+      </c>
+      <c r="B171" s="46">
+        <v>1</v>
+      </c>
+      <c r="C171" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" s="46">
+        <v>1</v>
+      </c>
+      <c r="E171" s="46">
+        <v>2</v>
+      </c>
+      <c r="F171" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G171" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H171" s="46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="46">
+        <v>6</v>
+      </c>
+      <c r="B172" s="46">
+        <v>1</v>
+      </c>
+      <c r="C172" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="46">
+        <v>1</v>
+      </c>
+      <c r="E172" s="46">
+        <v>2</v>
+      </c>
+      <c r="F172" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G172" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H172" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="46">
+        <v>6</v>
+      </c>
+      <c r="B173" s="46">
+        <v>1</v>
+      </c>
+      <c r="C173" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173" s="46">
+        <v>1</v>
+      </c>
+      <c r="E173" s="46">
+        <v>2</v>
+      </c>
+      <c r="F173" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G173" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="H173" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="46">
+        <v>6</v>
+      </c>
+      <c r="B174" s="46">
+        <v>1</v>
+      </c>
+      <c r="C174" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174" s="46">
+        <v>1</v>
+      </c>
+      <c r="E174" s="46">
+        <v>2</v>
+      </c>
+      <c r="F174" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G174" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H174" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="46">
+        <v>6</v>
+      </c>
+      <c r="B175" s="46">
+        <v>1</v>
+      </c>
+      <c r="C175" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D175" s="45">
+        <v>2</v>
+      </c>
+      <c r="E175" s="45">
+        <v>4</v>
+      </c>
+      <c r="F175" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="G175" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H175" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="46">
+        <v>6</v>
+      </c>
+      <c r="B176" s="46">
+        <v>1</v>
+      </c>
+      <c r="C176" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D176" s="45">
+        <v>2</v>
+      </c>
+      <c r="E176" s="45">
+        <v>4</v>
+      </c>
+      <c r="F176" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="G176" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H176" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="46">
+        <v>6</v>
+      </c>
+      <c r="B177" s="46">
+        <v>1</v>
+      </c>
+      <c r="C177" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D177" s="45">
+        <v>2</v>
+      </c>
+      <c r="E177" s="45">
+        <v>4</v>
+      </c>
+      <c r="F177" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="G177" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H177" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="46">
+        <v>6</v>
+      </c>
+      <c r="B178" s="46">
+        <v>1</v>
+      </c>
+      <c r="C178" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D178" s="45">
+        <v>3</v>
+      </c>
+      <c r="E178" s="45">
+        <v>4</v>
+      </c>
+      <c r="F178" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="G178" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H178" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="46">
+        <v>6</v>
+      </c>
+      <c r="B179" s="46">
+        <v>1</v>
+      </c>
+      <c r="C179" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D179" s="45">
+        <v>3</v>
+      </c>
+      <c r="E179" s="45">
+        <v>4</v>
+      </c>
+      <c r="F179" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="G179" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H179" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="46">
+        <v>6</v>
+      </c>
+      <c r="B180" s="46">
+        <v>1</v>
+      </c>
+      <c r="C180" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D180" s="45">
+        <v>3</v>
+      </c>
+      <c r="E180" s="45">
+        <v>4</v>
+      </c>
+      <c r="F180" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="G180" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H180" s="45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="46">
+        <v>6</v>
+      </c>
+      <c r="B181" s="46">
+        <v>1</v>
+      </c>
+      <c r="C181" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D181" s="45">
+        <v>4</v>
+      </c>
+      <c r="E181" s="45">
+        <v>3</v>
+      </c>
+      <c r="F181" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="G181" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H181" s="45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="46">
+        <v>6</v>
+      </c>
+      <c r="B182" s="46">
+        <v>1</v>
+      </c>
+      <c r="C182" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D182" s="45">
+        <v>4</v>
+      </c>
+      <c r="E182" s="45">
+        <v>3</v>
+      </c>
+      <c r="F182" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="G182" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H182" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="46">
+        <v>6</v>
+      </c>
+      <c r="B183" s="46">
+        <v>1</v>
+      </c>
+      <c r="C183" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D183" s="45">
+        <v>4</v>
+      </c>
+      <c r="E183" s="45">
+        <v>3</v>
+      </c>
+      <c r="F183" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G183" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H183" s="45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="46">
+        <v>6</v>
+      </c>
+      <c r="B184" s="45">
+        <v>2</v>
+      </c>
+      <c r="C184" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184" s="46">
+        <v>1</v>
+      </c>
+      <c r="E184" s="46">
+        <v>2</v>
+      </c>
+      <c r="F184" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G184" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H184" s="45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="46">
+        <v>6</v>
+      </c>
+      <c r="B185" s="45">
+        <v>2</v>
+      </c>
+      <c r="C185" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D185" s="46">
+        <v>1</v>
+      </c>
+      <c r="E185" s="46">
+        <v>2</v>
+      </c>
+      <c r="F185" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G185" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H185" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="46">
+        <v>6</v>
+      </c>
+      <c r="B186" s="45">
+        <v>2</v>
+      </c>
+      <c r="C186" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D186" s="46">
+        <v>1</v>
+      </c>
+      <c r="E186" s="46">
+        <v>2</v>
+      </c>
+      <c r="F186" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G186" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H186" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="46">
+        <v>6</v>
+      </c>
+      <c r="B187" s="45">
+        <v>2</v>
+      </c>
+      <c r="C187" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D187" s="46">
+        <v>1</v>
+      </c>
+      <c r="E187" s="46">
+        <v>2</v>
+      </c>
+      <c r="F187" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="G187" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H187" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="46">
+        <v>6</v>
+      </c>
+      <c r="B188" s="45">
+        <v>2</v>
+      </c>
+      <c r="C188" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D188" s="46">
+        <v>1</v>
+      </c>
+      <c r="E188" s="46">
+        <v>2</v>
+      </c>
+      <c r="F188" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="G188" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H188" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="46">
+        <v>6</v>
+      </c>
+      <c r="B189" s="45">
+        <v>2</v>
+      </c>
+      <c r="C189" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189" s="46">
+        <v>1</v>
+      </c>
+      <c r="E189" s="46">
+        <v>2</v>
+      </c>
+      <c r="F189" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G189" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H189" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="46">
+        <v>6</v>
+      </c>
+      <c r="B190" s="45">
+        <v>2</v>
+      </c>
+      <c r="C190" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D190" s="45">
+        <v>2</v>
+      </c>
+      <c r="E190" s="45">
+        <v>4</v>
+      </c>
+      <c r="F190" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="G190" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H190" s="45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="46">
+        <v>6</v>
+      </c>
+      <c r="B191" s="45">
+        <v>2</v>
+      </c>
+      <c r="C191" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D191" s="45">
+        <v>2</v>
+      </c>
+      <c r="E191" s="45">
+        <v>4</v>
+      </c>
+      <c r="F191" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G191" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H191" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="46">
+        <v>6</v>
+      </c>
+      <c r="B192" s="45">
+        <v>2</v>
+      </c>
+      <c r="C192" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D192" s="45">
+        <v>2</v>
+      </c>
+      <c r="E192" s="45">
+        <v>4</v>
+      </c>
+      <c r="F192" s="45" t="s">
+        <v>355</v>
+      </c>
+      <c r="G192" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" s="45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="46">
+        <v>6</v>
+      </c>
+      <c r="B193" s="45">
+        <v>2</v>
+      </c>
+      <c r="C193" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D193" s="45">
+        <v>3</v>
+      </c>
+      <c r="E193" s="45">
+        <v>4</v>
+      </c>
+      <c r="F193" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="G193" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H193" s="45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="46">
+        <v>6</v>
+      </c>
+      <c r="B194" s="45">
+        <v>2</v>
+      </c>
+      <c r="C194" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D194" s="45">
+        <v>3</v>
+      </c>
+      <c r="E194" s="45">
+        <v>4</v>
+      </c>
+      <c r="F194" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G194" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H194" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="46">
+        <v>6</v>
+      </c>
+      <c r="B195" s="45">
+        <v>2</v>
+      </c>
+      <c r="C195" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D195" s="45">
+        <v>3</v>
+      </c>
+      <c r="E195" s="45">
+        <v>4</v>
+      </c>
+      <c r="F195" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="G195" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H195" s="45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="46">
+        <v>6</v>
+      </c>
+      <c r="B196" s="45">
+        <v>2</v>
+      </c>
+      <c r="C196" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D196" s="45">
+        <v>4</v>
+      </c>
+      <c r="E196" s="45">
+        <v>5</v>
+      </c>
+      <c r="F196" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="G196" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H196" s="45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="46">
+        <v>6</v>
+      </c>
+      <c r="B197" s="45">
+        <v>2</v>
+      </c>
+      <c r="C197" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D197" s="45">
+        <v>4</v>
+      </c>
+      <c r="E197" s="45">
+        <v>5</v>
+      </c>
+      <c r="F197" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G197" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H197" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="46">
+        <v>6</v>
+      </c>
+      <c r="B198" s="45">
+        <v>2</v>
+      </c>
+      <c r="C198" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D198" s="45">
+        <v>4</v>
+      </c>
+      <c r="E198" s="45">
+        <v>5</v>
+      </c>
+      <c r="F198" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="G198" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="H198" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="46">
+        <v>6</v>
+      </c>
+      <c r="B199" s="45">
+        <v>2</v>
+      </c>
+      <c r="C199" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D199" s="45">
+        <v>4</v>
+      </c>
+      <c r="E199" s="45">
+        <v>5</v>
+      </c>
+      <c r="F199" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G199" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H199" s="45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="46">
+        <v>6</v>
+      </c>
+      <c r="B200" s="45">
+        <v>2</v>
+      </c>
+      <c r="C200" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D200" s="45">
+        <v>4</v>
+      </c>
+      <c r="E200" s="45">
+        <v>5</v>
+      </c>
+      <c r="F200" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="G200" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H200" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="46">
+        <v>6</v>
+      </c>
+      <c r="B201" s="45">
+        <v>2</v>
+      </c>
+      <c r="C201" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D201" s="45">
+        <v>4</v>
+      </c>
+      <c r="E201" s="45">
+        <v>5</v>
+      </c>
+      <c r="F201" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="G201" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H201" s="45">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -9902,7 +10803,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H328"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -17123,10 +18024,1258 @@
         <v>20</v>
       </c>
     </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" s="46">
+        <v>7</v>
+      </c>
+      <c r="B281" s="46">
+        <v>1</v>
+      </c>
+      <c r="C281" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D281" s="46">
+        <v>1</v>
+      </c>
+      <c r="E281" s="46">
+        <v>2</v>
+      </c>
+      <c r="F281" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G281" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H281" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" s="46">
+        <v>7</v>
+      </c>
+      <c r="B282" s="46">
+        <v>1</v>
+      </c>
+      <c r="C282" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D282" s="46">
+        <v>1</v>
+      </c>
+      <c r="E282" s="46">
+        <v>2</v>
+      </c>
+      <c r="F282" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G282" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H282" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" s="46">
+        <v>7</v>
+      </c>
+      <c r="B283" s="46">
+        <v>1</v>
+      </c>
+      <c r="C283" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D283" s="46">
+        <v>1</v>
+      </c>
+      <c r="E283" s="46">
+        <v>2</v>
+      </c>
+      <c r="F283" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G283" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H283" s="46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" s="46">
+        <v>7</v>
+      </c>
+      <c r="B284" s="46">
+        <v>1</v>
+      </c>
+      <c r="C284" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D284" s="46">
+        <v>1</v>
+      </c>
+      <c r="E284" s="46">
+        <v>2</v>
+      </c>
+      <c r="F284" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G284" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H284" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" s="46">
+        <v>7</v>
+      </c>
+      <c r="B285" s="46">
+        <v>1</v>
+      </c>
+      <c r="C285" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D285" s="46">
+        <v>1</v>
+      </c>
+      <c r="E285" s="46">
+        <v>2</v>
+      </c>
+      <c r="F285" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G285" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="H285" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" s="46">
+        <v>7</v>
+      </c>
+      <c r="B286" s="46">
+        <v>1</v>
+      </c>
+      <c r="C286" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D286" s="46">
+        <v>1</v>
+      </c>
+      <c r="E286" s="46">
+        <v>2</v>
+      </c>
+      <c r="F286" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G286" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H286" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287" s="46">
+        <v>7</v>
+      </c>
+      <c r="B287" s="46">
+        <v>1</v>
+      </c>
+      <c r="C287" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D287" s="45">
+        <v>2</v>
+      </c>
+      <c r="E287" s="45">
+        <v>4</v>
+      </c>
+      <c r="F287" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="G287" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H287" s="45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A288" s="46">
+        <v>7</v>
+      </c>
+      <c r="B288" s="46">
+        <v>1</v>
+      </c>
+      <c r="C288" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D288" s="45">
+        <v>2</v>
+      </c>
+      <c r="E288" s="45">
+        <v>4</v>
+      </c>
+      <c r="F288" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="G288" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H288" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" s="46">
+        <v>7</v>
+      </c>
+      <c r="B289" s="46">
+        <v>1</v>
+      </c>
+      <c r="C289" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D289" s="45">
+        <v>2</v>
+      </c>
+      <c r="E289" s="45">
+        <v>4</v>
+      </c>
+      <c r="F289" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="G289" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H289" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290" s="46">
+        <v>7</v>
+      </c>
+      <c r="B290" s="46">
+        <v>1</v>
+      </c>
+      <c r="C290" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D290" s="45">
+        <v>3</v>
+      </c>
+      <c r="E290" s="45">
+        <v>4</v>
+      </c>
+      <c r="F290" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="G290" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H290" s="45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291" s="46">
+        <v>7</v>
+      </c>
+      <c r="B291" s="46">
+        <v>1</v>
+      </c>
+      <c r="C291" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D291" s="45">
+        <v>3</v>
+      </c>
+      <c r="E291" s="45">
+        <v>4</v>
+      </c>
+      <c r="F291" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="G291" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H291" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292" s="46">
+        <v>7</v>
+      </c>
+      <c r="B292" s="46">
+        <v>1</v>
+      </c>
+      <c r="C292" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D292" s="45">
+        <v>3</v>
+      </c>
+      <c r="E292" s="45">
+        <v>4</v>
+      </c>
+      <c r="F292" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="G292" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H292" s="45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293" s="46">
+        <v>7</v>
+      </c>
+      <c r="B293" s="46">
+        <v>1</v>
+      </c>
+      <c r="C293" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D293" s="45">
+        <v>4</v>
+      </c>
+      <c r="E293" s="45">
+        <v>3</v>
+      </c>
+      <c r="F293" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="G293" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H293" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A294" s="46">
+        <v>7</v>
+      </c>
+      <c r="B294" s="46">
+        <v>1</v>
+      </c>
+      <c r="C294" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D294" s="45">
+        <v>4</v>
+      </c>
+      <c r="E294" s="45">
+        <v>3</v>
+      </c>
+      <c r="F294" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="G294" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H294" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295" s="46">
+        <v>7</v>
+      </c>
+      <c r="B295" s="46">
+        <v>1</v>
+      </c>
+      <c r="C295" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D295" s="45">
+        <v>4</v>
+      </c>
+      <c r="E295" s="45">
+        <v>3</v>
+      </c>
+      <c r="F295" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G295" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H295" s="45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296" s="46">
+        <v>7</v>
+      </c>
+      <c r="B296" s="45">
+        <v>2</v>
+      </c>
+      <c r="C296" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D296" s="46">
+        <v>1</v>
+      </c>
+      <c r="E296" s="46">
+        <v>2</v>
+      </c>
+      <c r="F296" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G296" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H296" s="45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" s="46">
+        <v>7</v>
+      </c>
+      <c r="B297" s="45">
+        <v>2</v>
+      </c>
+      <c r="C297" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D297" s="46">
+        <v>1</v>
+      </c>
+      <c r="E297" s="46">
+        <v>2</v>
+      </c>
+      <c r="F297" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G297" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H297" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298" s="46">
+        <v>7</v>
+      </c>
+      <c r="B298" s="45">
+        <v>2</v>
+      </c>
+      <c r="C298" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D298" s="46">
+        <v>1</v>
+      </c>
+      <c r="E298" s="46">
+        <v>2</v>
+      </c>
+      <c r="F298" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G298" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H298" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" s="46">
+        <v>7</v>
+      </c>
+      <c r="B299" s="45">
+        <v>2</v>
+      </c>
+      <c r="C299" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D299" s="46">
+        <v>1</v>
+      </c>
+      <c r="E299" s="46">
+        <v>2</v>
+      </c>
+      <c r="F299" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="G299" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H299" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" s="46">
+        <v>7</v>
+      </c>
+      <c r="B300" s="45">
+        <v>2</v>
+      </c>
+      <c r="C300" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D300" s="46">
+        <v>1</v>
+      </c>
+      <c r="E300" s="46">
+        <v>2</v>
+      </c>
+      <c r="F300" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="G300" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H300" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" s="46">
+        <v>7</v>
+      </c>
+      <c r="B301" s="45">
+        <v>2</v>
+      </c>
+      <c r="C301" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D301" s="46">
+        <v>1</v>
+      </c>
+      <c r="E301" s="46">
+        <v>2</v>
+      </c>
+      <c r="F301" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G301" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H301" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" s="46">
+        <v>7</v>
+      </c>
+      <c r="B302" s="45">
+        <v>2</v>
+      </c>
+      <c r="C302" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D302" s="45">
+        <v>2</v>
+      </c>
+      <c r="E302" s="45">
+        <v>4</v>
+      </c>
+      <c r="F302" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="G302" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H302" s="45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" s="46">
+        <v>7</v>
+      </c>
+      <c r="B303" s="45">
+        <v>2</v>
+      </c>
+      <c r="C303" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D303" s="45">
+        <v>2</v>
+      </c>
+      <c r="E303" s="45">
+        <v>4</v>
+      </c>
+      <c r="F303" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G303" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H303" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" s="46">
+        <v>7</v>
+      </c>
+      <c r="B304" s="45">
+        <v>2</v>
+      </c>
+      <c r="C304" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D304" s="45">
+        <v>2</v>
+      </c>
+      <c r="E304" s="45">
+        <v>4</v>
+      </c>
+      <c r="F304" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="G304" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H304" s="45" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" s="46">
+        <v>7</v>
+      </c>
+      <c r="B305" s="45">
+        <v>2</v>
+      </c>
+      <c r="C305" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D305" s="45">
+        <v>3</v>
+      </c>
+      <c r="E305" s="45">
+        <v>4</v>
+      </c>
+      <c r="F305" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="G305" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H305" s="45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" s="46">
+        <v>7</v>
+      </c>
+      <c r="B306" s="45">
+        <v>2</v>
+      </c>
+      <c r="C306" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D306" s="45">
+        <v>3</v>
+      </c>
+      <c r="E306" s="45">
+        <v>4</v>
+      </c>
+      <c r="F306" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G306" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H306" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" s="46">
+        <v>7</v>
+      </c>
+      <c r="B307" s="45">
+        <v>2</v>
+      </c>
+      <c r="C307" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D307" s="45">
+        <v>3</v>
+      </c>
+      <c r="E307" s="45">
+        <v>4</v>
+      </c>
+      <c r="F307" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="G307" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H307" s="45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" s="46">
+        <v>7</v>
+      </c>
+      <c r="B308" s="45">
+        <v>2</v>
+      </c>
+      <c r="C308" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D308" s="45">
+        <v>4</v>
+      </c>
+      <c r="E308" s="45">
+        <v>4</v>
+      </c>
+      <c r="F308" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="G308" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H308" s="45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" s="46">
+        <v>7</v>
+      </c>
+      <c r="B309" s="45">
+        <v>2</v>
+      </c>
+      <c r="C309" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D309" s="45">
+        <v>4</v>
+      </c>
+      <c r="E309" s="45">
+        <v>4</v>
+      </c>
+      <c r="F309" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G309" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H309" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" s="46">
+        <v>7</v>
+      </c>
+      <c r="B310" s="45">
+        <v>2</v>
+      </c>
+      <c r="C310" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D310" s="45">
+        <v>4</v>
+      </c>
+      <c r="E310" s="45">
+        <v>4</v>
+      </c>
+      <c r="F310" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="G310" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="H310" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" s="46">
+        <v>7</v>
+      </c>
+      <c r="B311" s="45">
+        <v>2</v>
+      </c>
+      <c r="C311" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D311" s="45">
+        <v>4</v>
+      </c>
+      <c r="E311" s="45">
+        <v>4</v>
+      </c>
+      <c r="F311" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G311" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H311" s="45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" s="46">
+        <v>7</v>
+      </c>
+      <c r="B312" s="45">
+        <v>2</v>
+      </c>
+      <c r="C312" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D312" s="45">
+        <v>4</v>
+      </c>
+      <c r="E312" s="45">
+        <v>4</v>
+      </c>
+      <c r="F312" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="G312" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H312" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" s="46">
+        <v>7</v>
+      </c>
+      <c r="B313" s="45">
+        <v>2</v>
+      </c>
+      <c r="C313" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D313" s="45">
+        <v>4</v>
+      </c>
+      <c r="E313" s="45">
+        <v>4</v>
+      </c>
+      <c r="F313" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="G313" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H313" s="45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" s="46">
+        <v>7</v>
+      </c>
+      <c r="B314" s="45">
+        <v>3</v>
+      </c>
+      <c r="C314" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D314" s="46">
+        <v>1</v>
+      </c>
+      <c r="E314" s="46">
+        <v>2</v>
+      </c>
+      <c r="F314" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G314" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H314" s="45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" s="46">
+        <v>7</v>
+      </c>
+      <c r="B315" s="45">
+        <v>3</v>
+      </c>
+      <c r="C315" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D315" s="46">
+        <v>1</v>
+      </c>
+      <c r="E315" s="46">
+        <v>2</v>
+      </c>
+      <c r="F315" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="G315" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H315" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" s="46">
+        <v>7</v>
+      </c>
+      <c r="B316" s="45">
+        <v>3</v>
+      </c>
+      <c r="C316" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D316" s="46">
+        <v>1</v>
+      </c>
+      <c r="E316" s="46">
+        <v>2</v>
+      </c>
+      <c r="F316" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="G316" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H316" s="45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" s="46">
+        <v>7</v>
+      </c>
+      <c r="B317" s="45">
+        <v>3</v>
+      </c>
+      <c r="C317" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D317" s="46">
+        <v>1</v>
+      </c>
+      <c r="E317" s="46">
+        <v>2</v>
+      </c>
+      <c r="F317" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="G317" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H317" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" s="46">
+        <v>7</v>
+      </c>
+      <c r="B318" s="45">
+        <v>3</v>
+      </c>
+      <c r="C318" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D318" s="46">
+        <v>1</v>
+      </c>
+      <c r="E318" s="46">
+        <v>2</v>
+      </c>
+      <c r="F318" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G318" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H318" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" s="46">
+        <v>7</v>
+      </c>
+      <c r="B319" s="45">
+        <v>3</v>
+      </c>
+      <c r="C319" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D319" s="46">
+        <v>1</v>
+      </c>
+      <c r="E319" s="46">
+        <v>2</v>
+      </c>
+      <c r="F319" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="G319" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H319" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" s="46">
+        <v>7</v>
+      </c>
+      <c r="B320" s="45">
+        <v>3</v>
+      </c>
+      <c r="C320" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D320" s="46">
+        <v>2</v>
+      </c>
+      <c r="E320" s="46">
+        <v>4</v>
+      </c>
+      <c r="F320" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="G320" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H320" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" s="46">
+        <v>7</v>
+      </c>
+      <c r="B321" s="45">
+        <v>3</v>
+      </c>
+      <c r="C321" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D321" s="46">
+        <v>2</v>
+      </c>
+      <c r="E321" s="46">
+        <v>4</v>
+      </c>
+      <c r="F321" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="G321" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H321" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" s="46">
+        <v>7</v>
+      </c>
+      <c r="B322" s="45">
+        <v>3</v>
+      </c>
+      <c r="C322" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D322" s="46">
+        <v>2</v>
+      </c>
+      <c r="E322" s="46">
+        <v>4</v>
+      </c>
+      <c r="F322" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G322" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H322" s="45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" s="46">
+        <v>7</v>
+      </c>
+      <c r="B323" s="45">
+        <v>3</v>
+      </c>
+      <c r="C323" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D323" s="46">
+        <v>3</v>
+      </c>
+      <c r="E323" s="46">
+        <v>4</v>
+      </c>
+      <c r="F323" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G323" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H323" s="46" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" s="46">
+        <v>7</v>
+      </c>
+      <c r="B324" s="45">
+        <v>3</v>
+      </c>
+      <c r="C324" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D324" s="46">
+        <v>3</v>
+      </c>
+      <c r="E324" s="46">
+        <v>4</v>
+      </c>
+      <c r="F324" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G324" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H324" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" s="46">
+        <v>7</v>
+      </c>
+      <c r="B325" s="45">
+        <v>3</v>
+      </c>
+      <c r="C325" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D325" s="46">
+        <v>3</v>
+      </c>
+      <c r="E325" s="46">
+        <v>4</v>
+      </c>
+      <c r="F325" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="G325" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H325" s="46">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" s="46">
+        <v>7</v>
+      </c>
+      <c r="B326" s="45">
+        <v>3</v>
+      </c>
+      <c r="C326" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D326" s="46">
+        <v>4</v>
+      </c>
+      <c r="E326" s="46">
+        <v>4</v>
+      </c>
+      <c r="F326" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="G326" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H326" s="46" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" s="46">
+        <v>7</v>
+      </c>
+      <c r="B327" s="45">
+        <v>3</v>
+      </c>
+      <c r="C327" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D327" s="46">
+        <v>4</v>
+      </c>
+      <c r="E327" s="46">
+        <v>4</v>
+      </c>
+      <c r="F327" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="G327" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H327" s="46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" s="46">
+        <v>7</v>
+      </c>
+      <c r="B328" s="45">
+        <v>3</v>
+      </c>
+      <c r="C328" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D328" s="46">
+        <v>4</v>
+      </c>
+      <c r="E328" s="46">
+        <v>4</v>
+      </c>
+      <c r="F328" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="G328" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H328" s="46">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C300" xr:uid="{00000000-0002-0000-0C00-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C328" xr:uid="{00000000-0002-0000-0C00-000000000000}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>
@@ -30705,7 +32854,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3989455-9EAC-421E-A77C-EE6854BACA60}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -32640,9 +34789,957 @@
       <c r="I73" s="88"/>
       <c r="J73" s="88"/>
     </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="46">
+        <v>3</v>
+      </c>
+      <c r="B74" s="33">
+        <v>1</v>
+      </c>
+      <c r="C74" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="33">
+        <v>1</v>
+      </c>
+      <c r="E74" s="33">
+        <v>2</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="G74" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H74" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I74" s="47"/>
+      <c r="J74" s="47"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="46">
+        <v>3</v>
+      </c>
+      <c r="B75" s="33">
+        <v>1</v>
+      </c>
+      <c r="C75" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="33">
+        <v>1</v>
+      </c>
+      <c r="E75" s="33">
+        <v>2</v>
+      </c>
+      <c r="F75" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="G75" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I75" s="47"/>
+      <c r="J75" s="47"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="46">
+        <v>3</v>
+      </c>
+      <c r="B76" s="33">
+        <v>1</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="33">
+        <v>1</v>
+      </c>
+      <c r="E76" s="33">
+        <v>2</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H76" s="33">
+        <v>10</v>
+      </c>
+      <c r="I76" s="47"/>
+      <c r="J76" s="47"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="46">
+        <v>3</v>
+      </c>
+      <c r="B77" s="33">
+        <v>1</v>
+      </c>
+      <c r="C77" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="33">
+        <v>1</v>
+      </c>
+      <c r="E77" s="33">
+        <v>2</v>
+      </c>
+      <c r="F77" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G77" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="33">
+        <v>8</v>
+      </c>
+      <c r="I77" s="47"/>
+      <c r="J77" s="47"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="46">
+        <v>3</v>
+      </c>
+      <c r="B78" s="33">
+        <v>1</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="33">
+        <v>1</v>
+      </c>
+      <c r="E78" s="33">
+        <v>2</v>
+      </c>
+      <c r="F78" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="G78" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="33">
+        <v>8</v>
+      </c>
+      <c r="I78" s="47"/>
+      <c r="J78" s="47"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="46">
+        <v>3</v>
+      </c>
+      <c r="B79" s="46">
+        <v>1</v>
+      </c>
+      <c r="C79" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D79" s="45"/>
+      <c r="E79" s="45"/>
+      <c r="F79" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="G79" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="45" t="s">
+        <v>609</v>
+      </c>
+      <c r="I79" s="47"/>
+      <c r="J79" s="47"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="46">
+        <v>3</v>
+      </c>
+      <c r="B80" s="46">
+        <v>1</v>
+      </c>
+      <c r="C80" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D80" s="45"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="G80" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="I80" s="47"/>
+      <c r="J80" s="47"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="46">
+        <v>3</v>
+      </c>
+      <c r="B81" s="46">
+        <v>1</v>
+      </c>
+      <c r="C81" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D81" s="45"/>
+      <c r="E81" s="45"/>
+      <c r="F81" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="G81" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H81" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="I81" s="47"/>
+      <c r="J81" s="47"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="46">
+        <v>3</v>
+      </c>
+      <c r="B82" s="46">
+        <v>1</v>
+      </c>
+      <c r="C82" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D82" s="45"/>
+      <c r="E82" s="45"/>
+      <c r="F82" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G82" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H82" s="45" t="s">
+        <v>609</v>
+      </c>
+      <c r="I82" s="47"/>
+      <c r="J82" s="47"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="46">
+        <v>3</v>
+      </c>
+      <c r="B83" s="46">
+        <v>1</v>
+      </c>
+      <c r="C83" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D83" s="45"/>
+      <c r="E83" s="45"/>
+      <c r="F83" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="G83" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H83" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="I83" s="47"/>
+      <c r="J83" s="47"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="46">
+        <v>3</v>
+      </c>
+      <c r="B84" s="46">
+        <v>1</v>
+      </c>
+      <c r="C84" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" s="45"/>
+      <c r="E84" s="45"/>
+      <c r="F84" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="G84" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" s="45" t="s">
+        <v>613</v>
+      </c>
+      <c r="I84" s="47"/>
+      <c r="J84" s="47"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="46">
+        <v>3</v>
+      </c>
+      <c r="B85" s="16">
+        <v>2</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="14">
+        <v>1</v>
+      </c>
+      <c r="E85" s="14">
+        <v>2</v>
+      </c>
+      <c r="F85" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" s="16">
+        <v>10</v>
+      </c>
+      <c r="I85" s="47"/>
+      <c r="J85" s="47"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="46">
+        <v>3</v>
+      </c>
+      <c r="B86" s="16">
+        <v>2</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="14">
+        <v>1</v>
+      </c>
+      <c r="E86" s="14">
+        <v>2</v>
+      </c>
+      <c r="F86" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H86" s="16">
+        <v>10</v>
+      </c>
+      <c r="I86" s="47"/>
+      <c r="J86" s="47"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="46">
+        <v>3</v>
+      </c>
+      <c r="B87" s="16">
+        <v>2</v>
+      </c>
+      <c r="C87" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="14">
+        <v>1</v>
+      </c>
+      <c r="E87" s="14">
+        <v>2</v>
+      </c>
+      <c r="F87" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I87" s="47"/>
+      <c r="J87" s="47"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="46">
+        <v>3</v>
+      </c>
+      <c r="B88" s="16">
+        <v>2</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="14">
+        <v>1</v>
+      </c>
+      <c r="E88" s="14">
+        <v>2</v>
+      </c>
+      <c r="F88" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G88" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H88" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I88" s="47"/>
+      <c r="J88" s="47"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="46">
+        <v>3</v>
+      </c>
+      <c r="B89" s="16">
+        <v>2</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="14">
+        <v>1</v>
+      </c>
+      <c r="E89" s="14">
+        <v>2</v>
+      </c>
+      <c r="F89" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H89" s="16">
+        <v>10</v>
+      </c>
+      <c r="I89" s="47"/>
+      <c r="J89" s="47"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="46">
+        <v>3</v>
+      </c>
+      <c r="B90" s="45">
+        <v>2</v>
+      </c>
+      <c r="C90" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" s="45"/>
+      <c r="E90" s="45"/>
+      <c r="F90" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="G90" s="45"/>
+      <c r="H90" s="45" t="s">
+        <v>609</v>
+      </c>
+      <c r="I90" s="47"/>
+      <c r="J90" s="47"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="46">
+        <v>3</v>
+      </c>
+      <c r="B91" s="45">
+        <v>2</v>
+      </c>
+      <c r="C91" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G91" s="45"/>
+      <c r="H91" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="I91" s="47"/>
+      <c r="J91" s="47"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="46">
+        <v>3</v>
+      </c>
+      <c r="B92" s="45">
+        <v>2</v>
+      </c>
+      <c r="C92" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="45"/>
+      <c r="E92" s="45"/>
+      <c r="F92" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="G92" s="45"/>
+      <c r="H92" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="I92" s="47"/>
+      <c r="J92" s="47"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="46">
+        <v>3</v>
+      </c>
+      <c r="B93" s="45">
+        <v>2</v>
+      </c>
+      <c r="C93" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D93" s="45"/>
+      <c r="E93" s="45"/>
+      <c r="F93" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="G93" s="45"/>
+      <c r="H93" s="45" t="s">
+        <v>581</v>
+      </c>
+      <c r="I93" s="47"/>
+      <c r="J93" s="47"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="46">
+        <v>3</v>
+      </c>
+      <c r="B94" s="45">
+        <v>2</v>
+      </c>
+      <c r="C94" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D94" s="45"/>
+      <c r="E94" s="45"/>
+      <c r="F94" s="45" t="s">
+        <v>610</v>
+      </c>
+      <c r="G94" s="45"/>
+      <c r="H94" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="I94" s="47"/>
+      <c r="J94" s="47"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="46">
+        <v>3</v>
+      </c>
+      <c r="B95" s="45">
+        <v>2</v>
+      </c>
+      <c r="C95" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D95" s="45"/>
+      <c r="E95" s="45"/>
+      <c r="F95" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="G95" s="45"/>
+      <c r="H95" s="45" t="s">
+        <v>354</v>
+      </c>
+      <c r="I95" s="47"/>
+      <c r="J95" s="47"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="46">
+        <v>3</v>
+      </c>
+      <c r="B96" s="18">
+        <v>3</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="17">
+        <v>1</v>
+      </c>
+      <c r="E96" s="17">
+        <v>2</v>
+      </c>
+      <c r="F96" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G96" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="18">
+        <v>10</v>
+      </c>
+      <c r="I96" s="47"/>
+      <c r="J96" s="47"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="46">
+        <v>3</v>
+      </c>
+      <c r="B97" s="18">
+        <v>3</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="17">
+        <v>1</v>
+      </c>
+      <c r="E97" s="17">
+        <v>2</v>
+      </c>
+      <c r="F97" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G97" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H97" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="I97" s="47"/>
+      <c r="J97" s="47"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="46">
+        <v>3</v>
+      </c>
+      <c r="B98" s="18">
+        <v>3</v>
+      </c>
+      <c r="C98" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="17">
+        <v>1</v>
+      </c>
+      <c r="E98" s="17">
+        <v>2</v>
+      </c>
+      <c r="F98" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G98" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I98" s="47"/>
+      <c r="J98" s="47"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="46">
+        <v>3</v>
+      </c>
+      <c r="B99" s="18">
+        <v>3</v>
+      </c>
+      <c r="C99" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="17">
+        <v>1</v>
+      </c>
+      <c r="E99" s="17">
+        <v>2</v>
+      </c>
+      <c r="F99" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="G99" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H99" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" s="47"/>
+      <c r="J99" s="47"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="46">
+        <v>3</v>
+      </c>
+      <c r="B100" s="18">
+        <v>3</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="17">
+        <v>1</v>
+      </c>
+      <c r="E100" s="17">
+        <v>2</v>
+      </c>
+      <c r="F100" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="G100" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H100" s="18">
+        <v>8</v>
+      </c>
+      <c r="I100" s="47"/>
+      <c r="J100" s="47"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="46">
+        <v>3</v>
+      </c>
+      <c r="B101" s="45">
+        <v>3</v>
+      </c>
+      <c r="C101" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D101" s="45">
+        <v>2</v>
+      </c>
+      <c r="E101" s="45">
+        <v>3</v>
+      </c>
+      <c r="F101" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="G101" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H101" s="45" t="s">
+        <v>609</v>
+      </c>
+      <c r="I101" s="47"/>
+      <c r="J101" s="47"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="46">
+        <v>3</v>
+      </c>
+      <c r="B102" s="45">
+        <v>3</v>
+      </c>
+      <c r="C102" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D102" s="45">
+        <v>2</v>
+      </c>
+      <c r="E102" s="45">
+        <v>3</v>
+      </c>
+      <c r="F102" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="G102" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="I102" s="47"/>
+      <c r="J102" s="47"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="46">
+        <v>3</v>
+      </c>
+      <c r="B103" s="45">
+        <v>3</v>
+      </c>
+      <c r="C103" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D103" s="45">
+        <v>2</v>
+      </c>
+      <c r="E103" s="45">
+        <v>3</v>
+      </c>
+      <c r="F103" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="G103" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I103" s="47"/>
+      <c r="J103" s="47"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="46">
+        <v>3</v>
+      </c>
+      <c r="B104" s="45">
+        <v>3</v>
+      </c>
+      <c r="C104" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D104" s="45">
+        <v>3</v>
+      </c>
+      <c r="E104" s="45">
+        <v>3</v>
+      </c>
+      <c r="F104" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="G104" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H104" s="45">
+        <v>8</v>
+      </c>
+      <c r="I104" s="47"/>
+      <c r="J104" s="47"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="46">
+        <v>3</v>
+      </c>
+      <c r="B105" s="45">
+        <v>3</v>
+      </c>
+      <c r="C105" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D105" s="45">
+        <v>3</v>
+      </c>
+      <c r="E105" s="45">
+        <v>3</v>
+      </c>
+      <c r="F105" s="45" t="s">
+        <v>611</v>
+      </c>
+      <c r="G105" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H105" s="45">
+        <v>10</v>
+      </c>
+      <c r="I105" s="47"/>
+      <c r="J105" s="47"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="46">
+        <v>3</v>
+      </c>
+      <c r="B106" s="45">
+        <v>3</v>
+      </c>
+      <c r="C106" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D106" s="45">
+        <v>3</v>
+      </c>
+      <c r="E106" s="45">
+        <v>3</v>
+      </c>
+      <c r="F106" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" s="45">
+        <v>14</v>
+      </c>
+      <c r="I106" s="47"/>
+      <c r="J106" s="47"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="46">
+        <v>3</v>
+      </c>
+      <c r="B107" s="45">
+        <v>3</v>
+      </c>
+      <c r="C107" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D107" s="45">
+        <v>4</v>
+      </c>
+      <c r="E107" s="45">
+        <v>3</v>
+      </c>
+      <c r="F107" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="G107" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H107" s="45">
+        <v>10</v>
+      </c>
+      <c r="I107" s="47"/>
+      <c r="J107" s="47"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="46">
+        <v>3</v>
+      </c>
+      <c r="B108" s="45">
+        <v>3</v>
+      </c>
+      <c r="C108" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D108" s="45">
+        <v>4</v>
+      </c>
+      <c r="E108" s="45">
+        <v>3</v>
+      </c>
+      <c r="F108" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="G108" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="I108" s="47"/>
+      <c r="J108" s="47"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="46">
+        <v>3</v>
+      </c>
+      <c r="B109" s="45">
+        <v>3</v>
+      </c>
+      <c r="C109" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D109" s="45">
+        <v>4</v>
+      </c>
+      <c r="E109" s="45">
+        <v>3</v>
+      </c>
+      <c r="F109" s="45" t="s">
+        <v>612</v>
+      </c>
+      <c r="G109" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109" s="47"/>
+      <c r="J109" s="47"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C73" xr:uid="{6CEDAECB-0314-4A24-8A52-C968EE7D790B}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C109" xr:uid="{6CEDAECB-0314-4A24-8A52-C968EE7D790B}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>
@@ -33811,8 +36908,17 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AADD0C13-114C-4ED4-B379-C4CDC7C1E2DB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -33987,6 +37093,14 @@
         <v>564</v>
       </c>
     </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>603</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>602</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33995,7 +37109,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I312"/>
+  <dimension ref="A1:I355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -41832,9 +44946,1087 @@
       </c>
       <c r="I312" s="63"/>
     </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="46">
+        <v>8</v>
+      </c>
+      <c r="B313" s="46">
+        <v>1</v>
+      </c>
+      <c r="C313" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D313" s="46">
+        <v>1</v>
+      </c>
+      <c r="E313" s="46">
+        <v>2</v>
+      </c>
+      <c r="F313" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G313" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H313" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="46">
+        <v>8</v>
+      </c>
+      <c r="B314" s="46">
+        <v>1</v>
+      </c>
+      <c r="C314" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D314" s="46">
+        <v>1</v>
+      </c>
+      <c r="E314" s="46">
+        <v>2</v>
+      </c>
+      <c r="F314" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G314" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H314" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="46">
+        <v>8</v>
+      </c>
+      <c r="B315" s="46">
+        <v>1</v>
+      </c>
+      <c r="C315" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D315" s="46">
+        <v>1</v>
+      </c>
+      <c r="E315" s="46">
+        <v>2</v>
+      </c>
+      <c r="F315" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G315" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H315" s="46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="46">
+        <v>8</v>
+      </c>
+      <c r="B316" s="46">
+        <v>1</v>
+      </c>
+      <c r="C316" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D316" s="46">
+        <v>1</v>
+      </c>
+      <c r="E316" s="46">
+        <v>2</v>
+      </c>
+      <c r="F316" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G316" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H316" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="46">
+        <v>8</v>
+      </c>
+      <c r="B317" s="46">
+        <v>1</v>
+      </c>
+      <c r="C317" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D317" s="46">
+        <v>1</v>
+      </c>
+      <c r="E317" s="46">
+        <v>2</v>
+      </c>
+      <c r="F317" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G317" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="H317" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="46">
+        <v>8</v>
+      </c>
+      <c r="B318" s="46">
+        <v>1</v>
+      </c>
+      <c r="C318" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D318" s="46">
+        <v>1</v>
+      </c>
+      <c r="E318" s="46">
+        <v>2</v>
+      </c>
+      <c r="F318" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G318" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H318" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="46">
+        <v>8</v>
+      </c>
+      <c r="B319" s="46">
+        <v>1</v>
+      </c>
+      <c r="C319" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D319" s="45"/>
+      <c r="E319" s="45"/>
+      <c r="F319" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="G319" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H319" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="46">
+        <v>8</v>
+      </c>
+      <c r="B320" s="46">
+        <v>1</v>
+      </c>
+      <c r="C320" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D320" s="45"/>
+      <c r="E320" s="45"/>
+      <c r="F320" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="G320" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H320" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" s="46">
+        <v>8</v>
+      </c>
+      <c r="B321" s="46">
+        <v>1</v>
+      </c>
+      <c r="C321" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D321" s="45"/>
+      <c r="E321" s="45"/>
+      <c r="F321" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G321" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H321" s="45" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" s="46">
+        <v>8</v>
+      </c>
+      <c r="B322" s="46">
+        <v>1</v>
+      </c>
+      <c r="C322" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D322" s="45"/>
+      <c r="E322" s="45"/>
+      <c r="F322" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="G322" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H322" s="45" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" s="46">
+        <v>8</v>
+      </c>
+      <c r="B323" s="46">
+        <v>1</v>
+      </c>
+      <c r="C323" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D323" s="45"/>
+      <c r="E323" s="45"/>
+      <c r="F323" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="G323" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H323" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" s="46">
+        <v>8</v>
+      </c>
+      <c r="B324" s="46">
+        <v>1</v>
+      </c>
+      <c r="C324" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D324" s="45"/>
+      <c r="E324" s="45"/>
+      <c r="F324" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="G324" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H324" s="45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" s="46">
+        <v>8</v>
+      </c>
+      <c r="B325" s="46">
+        <v>1</v>
+      </c>
+      <c r="C325" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D325" s="45">
+        <v>2</v>
+      </c>
+      <c r="E325" s="45">
+        <v>3</v>
+      </c>
+      <c r="F325" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="G325" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H325" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" s="46">
+        <v>8</v>
+      </c>
+      <c r="B326" s="46">
+        <v>1</v>
+      </c>
+      <c r="C326" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D326" s="45">
+        <v>2</v>
+      </c>
+      <c r="E326" s="45">
+        <v>3</v>
+      </c>
+      <c r="F326" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="G326" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H326" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" s="46">
+        <v>8</v>
+      </c>
+      <c r="B327" s="46">
+        <v>1</v>
+      </c>
+      <c r="C327" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D327" s="45">
+        <v>2</v>
+      </c>
+      <c r="E327" s="45">
+        <v>3</v>
+      </c>
+      <c r="F327" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G327" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H327" s="45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" s="46">
+        <v>8</v>
+      </c>
+      <c r="B328" s="45">
+        <v>2</v>
+      </c>
+      <c r="C328" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D328" s="46">
+        <v>1</v>
+      </c>
+      <c r="E328" s="46">
+        <v>2</v>
+      </c>
+      <c r="F328" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G328" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H328" s="45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329" s="46">
+        <v>8</v>
+      </c>
+      <c r="B329" s="45">
+        <v>2</v>
+      </c>
+      <c r="C329" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D329" s="46">
+        <v>1</v>
+      </c>
+      <c r="E329" s="46">
+        <v>2</v>
+      </c>
+      <c r="F329" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G329" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H329" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330" s="46">
+        <v>8</v>
+      </c>
+      <c r="B330" s="45">
+        <v>2</v>
+      </c>
+      <c r="C330" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D330" s="46">
+        <v>1</v>
+      </c>
+      <c r="E330" s="46">
+        <v>2</v>
+      </c>
+      <c r="F330" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G330" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H330" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331" s="46">
+        <v>8</v>
+      </c>
+      <c r="B331" s="45">
+        <v>2</v>
+      </c>
+      <c r="C331" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D331" s="46">
+        <v>1</v>
+      </c>
+      <c r="E331" s="46">
+        <v>2</v>
+      </c>
+      <c r="F331" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="G331" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H331" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" s="46">
+        <v>8</v>
+      </c>
+      <c r="B332" s="45">
+        <v>2</v>
+      </c>
+      <c r="C332" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D332" s="46">
+        <v>1</v>
+      </c>
+      <c r="E332" s="46">
+        <v>2</v>
+      </c>
+      <c r="F332" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="G332" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H332" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" s="46">
+        <v>8</v>
+      </c>
+      <c r="B333" s="45">
+        <v>2</v>
+      </c>
+      <c r="C333" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D333" s="46">
+        <v>1</v>
+      </c>
+      <c r="E333" s="46">
+        <v>2</v>
+      </c>
+      <c r="F333" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G333" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H333" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" s="46">
+        <v>8</v>
+      </c>
+      <c r="B334" s="45">
+        <v>2</v>
+      </c>
+      <c r="C334" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D334" s="45"/>
+      <c r="E334" s="45"/>
+      <c r="F334" s="45" t="s">
+        <v>355</v>
+      </c>
+      <c r="G334" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H334" s="45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" s="46">
+        <v>8</v>
+      </c>
+      <c r="B335" s="45">
+        <v>2</v>
+      </c>
+      <c r="C335" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D335" s="45"/>
+      <c r="E335" s="45"/>
+      <c r="F335" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="G335" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H335" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" s="46">
+        <v>8</v>
+      </c>
+      <c r="B336" s="45">
+        <v>2</v>
+      </c>
+      <c r="C336" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D336" s="45"/>
+      <c r="E336" s="45"/>
+      <c r="F336" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="G336" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H336" s="45" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A337" s="46">
+        <v>8</v>
+      </c>
+      <c r="B337" s="45">
+        <v>2</v>
+      </c>
+      <c r="C337" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D337" s="45"/>
+      <c r="E337" s="45"/>
+      <c r="F337" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="G337" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H337" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A338" s="46">
+        <v>8</v>
+      </c>
+      <c r="B338" s="45">
+        <v>2</v>
+      </c>
+      <c r="C338" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D338" s="45">
+        <v>2</v>
+      </c>
+      <c r="E338" s="45">
+        <v>4</v>
+      </c>
+      <c r="F338" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="G338" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H338" s="45" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A339" s="46">
+        <v>8</v>
+      </c>
+      <c r="B339" s="45">
+        <v>2</v>
+      </c>
+      <c r="C339" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D339" s="45">
+        <v>2</v>
+      </c>
+      <c r="E339" s="45">
+        <v>4</v>
+      </c>
+      <c r="F339" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="G339" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H339" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A340" s="46">
+        <v>8</v>
+      </c>
+      <c r="B340" s="45">
+        <v>3</v>
+      </c>
+      <c r="C340" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D340" s="46">
+        <v>1</v>
+      </c>
+      <c r="E340" s="46">
+        <v>2</v>
+      </c>
+      <c r="F340" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G340" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H340" s="45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341" s="46">
+        <v>8</v>
+      </c>
+      <c r="B341" s="45">
+        <v>3</v>
+      </c>
+      <c r="C341" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D341" s="46">
+        <v>1</v>
+      </c>
+      <c r="E341" s="46">
+        <v>2</v>
+      </c>
+      <c r="F341" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="G341" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H341" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A342" s="46">
+        <v>8</v>
+      </c>
+      <c r="B342" s="45">
+        <v>3</v>
+      </c>
+      <c r="C342" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D342" s="46">
+        <v>1</v>
+      </c>
+      <c r="E342" s="46">
+        <v>2</v>
+      </c>
+      <c r="F342" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="G342" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H342" s="45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A343" s="46">
+        <v>8</v>
+      </c>
+      <c r="B343" s="45">
+        <v>3</v>
+      </c>
+      <c r="C343" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D343" s="46">
+        <v>1</v>
+      </c>
+      <c r="E343" s="46">
+        <v>2</v>
+      </c>
+      <c r="F343" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="G343" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H343" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A344" s="46">
+        <v>8</v>
+      </c>
+      <c r="B344" s="45">
+        <v>3</v>
+      </c>
+      <c r="C344" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D344" s="46">
+        <v>1</v>
+      </c>
+      <c r="E344" s="46">
+        <v>2</v>
+      </c>
+      <c r="F344" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G344" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H344" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A345" s="46">
+        <v>8</v>
+      </c>
+      <c r="B345" s="45">
+        <v>3</v>
+      </c>
+      <c r="C345" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D345" s="46">
+        <v>1</v>
+      </c>
+      <c r="E345" s="46">
+        <v>2</v>
+      </c>
+      <c r="F345" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="G345" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H345" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A346" s="46">
+        <v>8</v>
+      </c>
+      <c r="B346" s="45">
+        <v>3</v>
+      </c>
+      <c r="C346" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D346" s="45">
+        <v>2</v>
+      </c>
+      <c r="E346" s="45">
+        <v>4</v>
+      </c>
+      <c r="F346" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="G346" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H346" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A347" s="46">
+        <v>8</v>
+      </c>
+      <c r="B347" s="45">
+        <v>3</v>
+      </c>
+      <c r="C347" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D347" s="45">
+        <v>2</v>
+      </c>
+      <c r="E347" s="45">
+        <v>4</v>
+      </c>
+      <c r="F347" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="G347" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H347" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A348" s="46">
+        <v>8</v>
+      </c>
+      <c r="B348" s="45">
+        <v>3</v>
+      </c>
+      <c r="C348" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D348" s="45">
+        <v>2</v>
+      </c>
+      <c r="E348" s="45">
+        <v>4</v>
+      </c>
+      <c r="F348" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="G348" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H348" s="45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A349" s="46">
+        <v>8</v>
+      </c>
+      <c r="B349" s="45">
+        <v>3</v>
+      </c>
+      <c r="C349" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D349" s="45">
+        <v>3</v>
+      </c>
+      <c r="E349" s="45">
+        <v>4</v>
+      </c>
+      <c r="F349" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="G349" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H349" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A350" s="46">
+        <v>8</v>
+      </c>
+      <c r="B350" s="45">
+        <v>3</v>
+      </c>
+      <c r="C350" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D350" s="45">
+        <v>3</v>
+      </c>
+      <c r="E350" s="45">
+        <v>4</v>
+      </c>
+      <c r="F350" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="G350" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H350" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A351" s="46">
+        <v>8</v>
+      </c>
+      <c r="B351" s="45">
+        <v>3</v>
+      </c>
+      <c r="C351" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D351" s="45">
+        <v>3</v>
+      </c>
+      <c r="E351" s="45">
+        <v>4</v>
+      </c>
+      <c r="F351" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="G351" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H351" s="45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A352" s="46">
+        <v>8</v>
+      </c>
+      <c r="B352" s="45">
+        <v>3</v>
+      </c>
+      <c r="C352" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D352" s="45">
+        <v>4</v>
+      </c>
+      <c r="E352" s="45">
+        <v>4</v>
+      </c>
+      <c r="F352" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="G352" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H352" s="45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" s="46">
+        <v>8</v>
+      </c>
+      <c r="B353" s="45">
+        <v>3</v>
+      </c>
+      <c r="C353" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D353" s="45">
+        <v>4</v>
+      </c>
+      <c r="E353" s="45">
+        <v>4</v>
+      </c>
+      <c r="F353" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="G353" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H353" s="45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A354" s="46">
+        <v>8</v>
+      </c>
+      <c r="B354" s="45">
+        <v>3</v>
+      </c>
+      <c r="C354" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D354" s="45">
+        <v>4</v>
+      </c>
+      <c r="E354" s="45">
+        <v>4</v>
+      </c>
+      <c r="F354" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="G354" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H354" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355" s="46">
+        <v>8</v>
+      </c>
+      <c r="B355" s="45">
+        <v>3</v>
+      </c>
+      <c r="C355" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D355" s="45">
+        <v>4</v>
+      </c>
+      <c r="E355" s="45">
+        <v>4</v>
+      </c>
+      <c r="F355" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="G355" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H355" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C312" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C355" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>
@@ -41844,7 +46036,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K293"/>
+  <dimension ref="A1:K336"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -49507,9 +53699,1087 @@
       </c>
       <c r="I293" s="63"/>
     </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="46">
+        <v>8</v>
+      </c>
+      <c r="B294" s="46">
+        <v>1</v>
+      </c>
+      <c r="C294" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D294" s="46">
+        <v>1</v>
+      </c>
+      <c r="E294" s="46">
+        <v>2</v>
+      </c>
+      <c r="F294" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G294" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H294" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="46">
+        <v>8</v>
+      </c>
+      <c r="B295" s="46">
+        <v>1</v>
+      </c>
+      <c r="C295" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D295" s="46">
+        <v>1</v>
+      </c>
+      <c r="E295" s="46">
+        <v>2</v>
+      </c>
+      <c r="F295" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G295" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H295" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="46">
+        <v>8</v>
+      </c>
+      <c r="B296" s="46">
+        <v>1</v>
+      </c>
+      <c r="C296" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D296" s="46">
+        <v>1</v>
+      </c>
+      <c r="E296" s="46">
+        <v>2</v>
+      </c>
+      <c r="F296" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G296" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H296" s="46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="46">
+        <v>8</v>
+      </c>
+      <c r="B297" s="46">
+        <v>1</v>
+      </c>
+      <c r="C297" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D297" s="46">
+        <v>1</v>
+      </c>
+      <c r="E297" s="46">
+        <v>2</v>
+      </c>
+      <c r="F297" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G297" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H297" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="46">
+        <v>8</v>
+      </c>
+      <c r="B298" s="46">
+        <v>1</v>
+      </c>
+      <c r="C298" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D298" s="46">
+        <v>1</v>
+      </c>
+      <c r="E298" s="46">
+        <v>2</v>
+      </c>
+      <c r="F298" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G298" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="H298" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="46">
+        <v>8</v>
+      </c>
+      <c r="B299" s="46">
+        <v>1</v>
+      </c>
+      <c r="C299" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D299" s="46">
+        <v>1</v>
+      </c>
+      <c r="E299" s="46">
+        <v>2</v>
+      </c>
+      <c r="F299" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G299" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H299" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="46">
+        <v>8</v>
+      </c>
+      <c r="B300" s="46">
+        <v>1</v>
+      </c>
+      <c r="C300" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D300" s="45"/>
+      <c r="E300" s="45"/>
+      <c r="F300" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="G300" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H300" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="46">
+        <v>8</v>
+      </c>
+      <c r="B301" s="46">
+        <v>1</v>
+      </c>
+      <c r="C301" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D301" s="45"/>
+      <c r="E301" s="45"/>
+      <c r="F301" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="G301" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H301" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="46">
+        <v>8</v>
+      </c>
+      <c r="B302" s="46">
+        <v>1</v>
+      </c>
+      <c r="C302" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D302" s="45"/>
+      <c r="E302" s="45"/>
+      <c r="F302" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G302" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H302" s="45" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="46">
+        <v>8</v>
+      </c>
+      <c r="B303" s="46">
+        <v>1</v>
+      </c>
+      <c r="C303" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D303" s="45"/>
+      <c r="E303" s="45"/>
+      <c r="F303" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="G303" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H303" s="45" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="46">
+        <v>8</v>
+      </c>
+      <c r="B304" s="46">
+        <v>1</v>
+      </c>
+      <c r="C304" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D304" s="45"/>
+      <c r="E304" s="45"/>
+      <c r="F304" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="G304" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H304" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" s="46">
+        <v>8</v>
+      </c>
+      <c r="B305" s="46">
+        <v>1</v>
+      </c>
+      <c r="C305" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D305" s="45"/>
+      <c r="E305" s="45"/>
+      <c r="F305" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="G305" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H305" s="45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" s="46">
+        <v>8</v>
+      </c>
+      <c r="B306" s="46">
+        <v>1</v>
+      </c>
+      <c r="C306" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D306" s="45">
+        <v>2</v>
+      </c>
+      <c r="E306" s="45">
+        <v>3</v>
+      </c>
+      <c r="F306" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="G306" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H306" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" s="46">
+        <v>8</v>
+      </c>
+      <c r="B307" s="46">
+        <v>1</v>
+      </c>
+      <c r="C307" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D307" s="45">
+        <v>2</v>
+      </c>
+      <c r="E307" s="45">
+        <v>3</v>
+      </c>
+      <c r="F307" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="G307" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H307" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" s="46">
+        <v>8</v>
+      </c>
+      <c r="B308" s="46">
+        <v>1</v>
+      </c>
+      <c r="C308" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D308" s="45">
+        <v>2</v>
+      </c>
+      <c r="E308" s="45">
+        <v>3</v>
+      </c>
+      <c r="F308" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G308" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H308" s="45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" s="46">
+        <v>8</v>
+      </c>
+      <c r="B309" s="45">
+        <v>2</v>
+      </c>
+      <c r="C309" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D309" s="46">
+        <v>1</v>
+      </c>
+      <c r="E309" s="46">
+        <v>2</v>
+      </c>
+      <c r="F309" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G309" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H309" s="45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" s="46">
+        <v>8</v>
+      </c>
+      <c r="B310" s="45">
+        <v>2</v>
+      </c>
+      <c r="C310" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D310" s="46">
+        <v>1</v>
+      </c>
+      <c r="E310" s="46">
+        <v>2</v>
+      </c>
+      <c r="F310" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G310" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H310" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" s="46">
+        <v>8</v>
+      </c>
+      <c r="B311" s="45">
+        <v>2</v>
+      </c>
+      <c r="C311" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D311" s="46">
+        <v>1</v>
+      </c>
+      <c r="E311" s="46">
+        <v>2</v>
+      </c>
+      <c r="F311" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G311" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H311" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" s="46">
+        <v>8</v>
+      </c>
+      <c r="B312" s="45">
+        <v>2</v>
+      </c>
+      <c r="C312" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D312" s="46">
+        <v>1</v>
+      </c>
+      <c r="E312" s="46">
+        <v>2</v>
+      </c>
+      <c r="F312" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="G312" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H312" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" s="46">
+        <v>8</v>
+      </c>
+      <c r="B313" s="45">
+        <v>2</v>
+      </c>
+      <c r="C313" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D313" s="46">
+        <v>1</v>
+      </c>
+      <c r="E313" s="46">
+        <v>2</v>
+      </c>
+      <c r="F313" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="G313" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H313" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" s="46">
+        <v>8</v>
+      </c>
+      <c r="B314" s="45">
+        <v>2</v>
+      </c>
+      <c r="C314" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D314" s="46">
+        <v>1</v>
+      </c>
+      <c r="E314" s="46">
+        <v>2</v>
+      </c>
+      <c r="F314" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G314" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H314" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" s="46">
+        <v>8</v>
+      </c>
+      <c r="B315" s="45">
+        <v>2</v>
+      </c>
+      <c r="C315" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D315" s="45"/>
+      <c r="E315" s="45"/>
+      <c r="F315" s="45" t="s">
+        <v>355</v>
+      </c>
+      <c r="G315" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H315" s="45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" s="46">
+        <v>8</v>
+      </c>
+      <c r="B316" s="45">
+        <v>2</v>
+      </c>
+      <c r="C316" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D316" s="45"/>
+      <c r="E316" s="45"/>
+      <c r="F316" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="G316" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H316" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" s="46">
+        <v>8</v>
+      </c>
+      <c r="B317" s="45">
+        <v>2</v>
+      </c>
+      <c r="C317" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D317" s="45"/>
+      <c r="E317" s="45"/>
+      <c r="F317" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="G317" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H317" s="45" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" s="46">
+        <v>8</v>
+      </c>
+      <c r="B318" s="45">
+        <v>2</v>
+      </c>
+      <c r="C318" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D318" s="45"/>
+      <c r="E318" s="45"/>
+      <c r="F318" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="G318" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H318" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" s="46">
+        <v>8</v>
+      </c>
+      <c r="B319" s="45">
+        <v>2</v>
+      </c>
+      <c r="C319" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D319" s="45">
+        <v>2</v>
+      </c>
+      <c r="E319" s="45">
+        <v>4</v>
+      </c>
+      <c r="F319" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="G319" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H319" s="45" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" s="46">
+        <v>8</v>
+      </c>
+      <c r="B320" s="45">
+        <v>2</v>
+      </c>
+      <c r="C320" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D320" s="45">
+        <v>2</v>
+      </c>
+      <c r="E320" s="45">
+        <v>4</v>
+      </c>
+      <c r="F320" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="G320" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H320" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" s="46">
+        <v>8</v>
+      </c>
+      <c r="B321" s="45">
+        <v>3</v>
+      </c>
+      <c r="C321" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D321" s="46">
+        <v>1</v>
+      </c>
+      <c r="E321" s="46">
+        <v>2</v>
+      </c>
+      <c r="F321" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G321" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H321" s="45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" s="46">
+        <v>8</v>
+      </c>
+      <c r="B322" s="45">
+        <v>3</v>
+      </c>
+      <c r="C322" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D322" s="46">
+        <v>1</v>
+      </c>
+      <c r="E322" s="46">
+        <v>2</v>
+      </c>
+      <c r="F322" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="G322" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H322" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" s="46">
+        <v>8</v>
+      </c>
+      <c r="B323" s="45">
+        <v>3</v>
+      </c>
+      <c r="C323" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D323" s="46">
+        <v>1</v>
+      </c>
+      <c r="E323" s="46">
+        <v>2</v>
+      </c>
+      <c r="F323" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="G323" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H323" s="45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" s="46">
+        <v>8</v>
+      </c>
+      <c r="B324" s="45">
+        <v>3</v>
+      </c>
+      <c r="C324" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D324" s="46">
+        <v>1</v>
+      </c>
+      <c r="E324" s="46">
+        <v>2</v>
+      </c>
+      <c r="F324" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="G324" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H324" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" s="46">
+        <v>8</v>
+      </c>
+      <c r="B325" s="45">
+        <v>3</v>
+      </c>
+      <c r="C325" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D325" s="46">
+        <v>1</v>
+      </c>
+      <c r="E325" s="46">
+        <v>2</v>
+      </c>
+      <c r="F325" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G325" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H325" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" s="46">
+        <v>8</v>
+      </c>
+      <c r="B326" s="45">
+        <v>3</v>
+      </c>
+      <c r="C326" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D326" s="46">
+        <v>1</v>
+      </c>
+      <c r="E326" s="46">
+        <v>2</v>
+      </c>
+      <c r="F326" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="G326" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H326" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" s="46">
+        <v>8</v>
+      </c>
+      <c r="B327" s="45">
+        <v>3</v>
+      </c>
+      <c r="C327" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D327" s="45">
+        <v>2</v>
+      </c>
+      <c r="E327" s="45">
+        <v>4</v>
+      </c>
+      <c r="F327" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="G327" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H327" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" s="46">
+        <v>8</v>
+      </c>
+      <c r="B328" s="45">
+        <v>3</v>
+      </c>
+      <c r="C328" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D328" s="45">
+        <v>2</v>
+      </c>
+      <c r="E328" s="45">
+        <v>4</v>
+      </c>
+      <c r="F328" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="G328" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H328" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329" s="46">
+        <v>8</v>
+      </c>
+      <c r="B329" s="45">
+        <v>3</v>
+      </c>
+      <c r="C329" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D329" s="45">
+        <v>2</v>
+      </c>
+      <c r="E329" s="45">
+        <v>4</v>
+      </c>
+      <c r="F329" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="G329" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H329" s="45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330" s="46">
+        <v>8</v>
+      </c>
+      <c r="B330" s="45">
+        <v>3</v>
+      </c>
+      <c r="C330" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D330" s="45">
+        <v>3</v>
+      </c>
+      <c r="E330" s="45">
+        <v>4</v>
+      </c>
+      <c r="F330" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="G330" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H330" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331" s="46">
+        <v>8</v>
+      </c>
+      <c r="B331" s="45">
+        <v>3</v>
+      </c>
+      <c r="C331" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D331" s="45">
+        <v>3</v>
+      </c>
+      <c r="E331" s="45">
+        <v>4</v>
+      </c>
+      <c r="F331" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="G331" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H331" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" s="46">
+        <v>8</v>
+      </c>
+      <c r="B332" s="45">
+        <v>3</v>
+      </c>
+      <c r="C332" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D332" s="45">
+        <v>3</v>
+      </c>
+      <c r="E332" s="45">
+        <v>4</v>
+      </c>
+      <c r="F332" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="G332" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H332" s="45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" s="46">
+        <v>8</v>
+      </c>
+      <c r="B333" s="45">
+        <v>3</v>
+      </c>
+      <c r="C333" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D333" s="45">
+        <v>4</v>
+      </c>
+      <c r="E333" s="45">
+        <v>4</v>
+      </c>
+      <c r="F333" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="G333" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H333" s="45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" s="46">
+        <v>8</v>
+      </c>
+      <c r="B334" s="45">
+        <v>3</v>
+      </c>
+      <c r="C334" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D334" s="45">
+        <v>4</v>
+      </c>
+      <c r="E334" s="45">
+        <v>4</v>
+      </c>
+      <c r="F334" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="G334" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H334" s="45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" s="46">
+        <v>8</v>
+      </c>
+      <c r="B335" s="45">
+        <v>3</v>
+      </c>
+      <c r="C335" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D335" s="45">
+        <v>4</v>
+      </c>
+      <c r="E335" s="45">
+        <v>4</v>
+      </c>
+      <c r="F335" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="G335" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H335" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" s="46">
+        <v>8</v>
+      </c>
+      <c r="B336" s="45">
+        <v>3</v>
+      </c>
+      <c r="C336" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D336" s="45">
+        <v>4</v>
+      </c>
+      <c r="E336" s="45">
+        <v>4</v>
+      </c>
+      <c r="F336" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="G336" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H336" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C293" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C336" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>
@@ -55358,7 +60628,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H390"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -63765,9 +69035,1343 @@
         <v>12</v>
       </c>
     </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A338" s="46">
+        <v>7</v>
+      </c>
+      <c r="B338" s="46">
+        <v>1</v>
+      </c>
+      <c r="C338" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D338" s="46">
+        <v>1</v>
+      </c>
+      <c r="E338" s="46">
+        <v>2</v>
+      </c>
+      <c r="F338" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G338" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H338" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A339" s="46">
+        <v>7</v>
+      </c>
+      <c r="B339" s="46">
+        <v>1</v>
+      </c>
+      <c r="C339" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D339" s="46">
+        <v>1</v>
+      </c>
+      <c r="E339" s="46">
+        <v>2</v>
+      </c>
+      <c r="F339" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G339" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H339" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A340" s="46">
+        <v>7</v>
+      </c>
+      <c r="B340" s="46">
+        <v>1</v>
+      </c>
+      <c r="C340" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D340" s="46">
+        <v>1</v>
+      </c>
+      <c r="E340" s="46">
+        <v>2</v>
+      </c>
+      <c r="F340" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G340" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H340" s="46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341" s="46">
+        <v>7</v>
+      </c>
+      <c r="B341" s="46">
+        <v>1</v>
+      </c>
+      <c r="C341" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D341" s="46">
+        <v>1</v>
+      </c>
+      <c r="E341" s="46">
+        <v>2</v>
+      </c>
+      <c r="F341" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G341" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H341" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A342" s="46">
+        <v>7</v>
+      </c>
+      <c r="B342" s="46">
+        <v>1</v>
+      </c>
+      <c r="C342" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D342" s="46">
+        <v>1</v>
+      </c>
+      <c r="E342" s="46">
+        <v>2</v>
+      </c>
+      <c r="F342" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G342" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H342" s="46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A343" s="46">
+        <v>7</v>
+      </c>
+      <c r="B343" s="46">
+        <v>1</v>
+      </c>
+      <c r="C343" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D343" s="45"/>
+      <c r="E343" s="45"/>
+      <c r="F343" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="G343" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H343" s="45" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A344" s="46">
+        <v>7</v>
+      </c>
+      <c r="B344" s="46">
+        <v>1</v>
+      </c>
+      <c r="C344" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D344" s="45"/>
+      <c r="E344" s="45"/>
+      <c r="F344" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="G344" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H344" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A345" s="46">
+        <v>7</v>
+      </c>
+      <c r="B345" s="46">
+        <v>1</v>
+      </c>
+      <c r="C345" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D345" s="45">
+        <v>2</v>
+      </c>
+      <c r="E345" s="45">
+        <v>4</v>
+      </c>
+      <c r="F345" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G345" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H345" s="45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A346" s="46">
+        <v>7</v>
+      </c>
+      <c r="B346" s="46">
+        <v>1</v>
+      </c>
+      <c r="C346" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D346" s="45">
+        <v>2</v>
+      </c>
+      <c r="E346" s="45">
+        <v>4</v>
+      </c>
+      <c r="F346" s="45" t="s">
+        <v>277</v>
+      </c>
+      <c r="G346" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H346" s="45" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A347" s="46">
+        <v>7</v>
+      </c>
+      <c r="B347" s="46">
+        <v>1</v>
+      </c>
+      <c r="C347" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D347" s="45"/>
+      <c r="E347" s="45"/>
+      <c r="F347" s="45" t="s">
+        <v>270</v>
+      </c>
+      <c r="G347" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H347" s="45" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A348" s="46">
+        <v>7</v>
+      </c>
+      <c r="B348" s="46">
+        <v>1</v>
+      </c>
+      <c r="C348" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D348" s="45">
+        <v>3</v>
+      </c>
+      <c r="E348" s="45">
+        <v>4</v>
+      </c>
+      <c r="F348" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="G348" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H348" s="45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A349" s="46">
+        <v>7</v>
+      </c>
+      <c r="B349" s="46">
+        <v>1</v>
+      </c>
+      <c r="C349" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D349" s="45">
+        <v>3</v>
+      </c>
+      <c r="E349" s="45">
+        <v>4</v>
+      </c>
+      <c r="F349" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G349" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H349" s="45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A350" s="46">
+        <v>7</v>
+      </c>
+      <c r="B350" s="46">
+        <v>1</v>
+      </c>
+      <c r="C350" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D350" s="45">
+        <v>3</v>
+      </c>
+      <c r="E350" s="45">
+        <v>4</v>
+      </c>
+      <c r="F350" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="G350" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H350" s="45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A351" s="46">
+        <v>7</v>
+      </c>
+      <c r="B351" s="45">
+        <v>2</v>
+      </c>
+      <c r="C351" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D351" s="46">
+        <v>1</v>
+      </c>
+      <c r="E351" s="46">
+        <v>2</v>
+      </c>
+      <c r="F351" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G351" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H351" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A352" s="46">
+        <v>7</v>
+      </c>
+      <c r="B352" s="45">
+        <v>2</v>
+      </c>
+      <c r="C352" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D352" s="46">
+        <v>1</v>
+      </c>
+      <c r="E352" s="46">
+        <v>2</v>
+      </c>
+      <c r="F352" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G352" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H352" s="45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" s="46">
+        <v>7</v>
+      </c>
+      <c r="B353" s="45">
+        <v>2</v>
+      </c>
+      <c r="C353" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D353" s="46">
+        <v>1</v>
+      </c>
+      <c r="E353" s="46">
+        <v>2</v>
+      </c>
+      <c r="F353" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G353" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H353" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A354" s="46">
+        <v>7</v>
+      </c>
+      <c r="B354" s="45">
+        <v>2</v>
+      </c>
+      <c r="C354" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D354" s="46">
+        <v>1</v>
+      </c>
+      <c r="E354" s="46">
+        <v>2</v>
+      </c>
+      <c r="F354" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G354" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H354" s="45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355" s="46">
+        <v>7</v>
+      </c>
+      <c r="B355" s="45">
+        <v>2</v>
+      </c>
+      <c r="C355" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D355" s="46">
+        <v>1</v>
+      </c>
+      <c r="E355" s="46">
+        <v>2</v>
+      </c>
+      <c r="F355" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="G355" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H355" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" s="46">
+        <v>7</v>
+      </c>
+      <c r="B356" s="45">
+        <v>2</v>
+      </c>
+      <c r="C356" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D356" s="45"/>
+      <c r="E356" s="45"/>
+      <c r="F356" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="G356" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H356" s="45" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A357" s="46">
+        <v>7</v>
+      </c>
+      <c r="B357" s="45">
+        <v>2</v>
+      </c>
+      <c r="C357" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D357" s="45"/>
+      <c r="E357" s="45"/>
+      <c r="F357" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="G357" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H357" s="45" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A358" s="46">
+        <v>7</v>
+      </c>
+      <c r="B358" s="45">
+        <v>2</v>
+      </c>
+      <c r="C358" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D358" s="45"/>
+      <c r="E358" s="45"/>
+      <c r="F358" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="G358" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H358" s="45" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359" s="46">
+        <v>7</v>
+      </c>
+      <c r="B359" s="45">
+        <v>2</v>
+      </c>
+      <c r="C359" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D359" s="45">
+        <v>2</v>
+      </c>
+      <c r="E359" s="45">
+        <v>4</v>
+      </c>
+      <c r="F359" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="G359" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H359" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" s="46">
+        <v>7</v>
+      </c>
+      <c r="B360" s="45">
+        <v>2</v>
+      </c>
+      <c r="C360" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D360" s="45">
+        <v>2</v>
+      </c>
+      <c r="E360" s="45">
+        <v>4</v>
+      </c>
+      <c r="F360" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G360" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H360" s="45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361" s="46">
+        <v>7</v>
+      </c>
+      <c r="B361" s="45">
+        <v>2</v>
+      </c>
+      <c r="C361" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D361" s="45">
+        <v>3</v>
+      </c>
+      <c r="E361" s="45">
+        <v>4</v>
+      </c>
+      <c r="F361" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="G361" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H361" s="45" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" s="46">
+        <v>7</v>
+      </c>
+      <c r="B362" s="45">
+        <v>2</v>
+      </c>
+      <c r="C362" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D362" s="45">
+        <v>3</v>
+      </c>
+      <c r="E362" s="45">
+        <v>4</v>
+      </c>
+      <c r="F362" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="G362" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H362" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" s="46">
+        <v>7</v>
+      </c>
+      <c r="B363" s="45">
+        <v>3</v>
+      </c>
+      <c r="C363" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D363" s="46">
+        <v>1</v>
+      </c>
+      <c r="E363" s="46">
+        <v>2</v>
+      </c>
+      <c r="F363" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="G363" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H363" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364" s="46">
+        <v>7</v>
+      </c>
+      <c r="B364" s="45">
+        <v>3</v>
+      </c>
+      <c r="C364" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D364" s="46">
+        <v>1</v>
+      </c>
+      <c r="E364" s="46">
+        <v>2</v>
+      </c>
+      <c r="F364" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="G364" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H364" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365" s="46">
+        <v>7</v>
+      </c>
+      <c r="B365" s="45">
+        <v>3</v>
+      </c>
+      <c r="C365" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D365" s="46">
+        <v>1</v>
+      </c>
+      <c r="E365" s="46">
+        <v>2</v>
+      </c>
+      <c r="F365" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G365" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H365" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366" s="46">
+        <v>7</v>
+      </c>
+      <c r="B366" s="45">
+        <v>3</v>
+      </c>
+      <c r="C366" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D366" s="46">
+        <v>1</v>
+      </c>
+      <c r="E366" s="46">
+        <v>2</v>
+      </c>
+      <c r="F366" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="G366" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="H366" s="45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367" s="46">
+        <v>7</v>
+      </c>
+      <c r="B367" s="45">
+        <v>3</v>
+      </c>
+      <c r="C367" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D367" s="46">
+        <v>1</v>
+      </c>
+      <c r="E367" s="46">
+        <v>2</v>
+      </c>
+      <c r="F367" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="G367" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H367" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A368" s="46">
+        <v>7</v>
+      </c>
+      <c r="B368" s="45">
+        <v>3</v>
+      </c>
+      <c r="C368" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D368" s="45"/>
+      <c r="E368" s="45"/>
+      <c r="F368" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="G368" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H368" s="45" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A369" s="46">
+        <v>7</v>
+      </c>
+      <c r="B369" s="45">
+        <v>3</v>
+      </c>
+      <c r="C369" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D369" s="45"/>
+      <c r="E369" s="45"/>
+      <c r="F369" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="G369" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H369" s="45" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A370" s="46">
+        <v>7</v>
+      </c>
+      <c r="B370" s="45">
+        <v>3</v>
+      </c>
+      <c r="C370" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D370" s="45"/>
+      <c r="E370" s="45"/>
+      <c r="F370" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="G370" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H370" s="45" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A371" s="46">
+        <v>7</v>
+      </c>
+      <c r="B371" s="45">
+        <v>3</v>
+      </c>
+      <c r="C371" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D371" s="45">
+        <v>2</v>
+      </c>
+      <c r="E371" s="45">
+        <v>3</v>
+      </c>
+      <c r="F371" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G371" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H371" s="45" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A372" s="46">
+        <v>7</v>
+      </c>
+      <c r="B372" s="45">
+        <v>3</v>
+      </c>
+      <c r="C372" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D372" s="45">
+        <v>2</v>
+      </c>
+      <c r="E372" s="45">
+        <v>3</v>
+      </c>
+      <c r="F372" s="45" t="s">
+        <v>277</v>
+      </c>
+      <c r="G372" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H372" s="45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A373" s="46">
+        <v>7</v>
+      </c>
+      <c r="B373" s="45">
+        <v>3</v>
+      </c>
+      <c r="C373" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D373" s="45">
+        <v>2</v>
+      </c>
+      <c r="E373" s="45">
+        <v>3</v>
+      </c>
+      <c r="F373" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G373" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H373" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A374" s="46">
+        <v>7</v>
+      </c>
+      <c r="B374" s="45">
+        <v>3</v>
+      </c>
+      <c r="C374" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D374" s="45">
+        <v>3</v>
+      </c>
+      <c r="E374" s="45">
+        <v>3</v>
+      </c>
+      <c r="F374" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="G374" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H374" s="45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A375" s="46">
+        <v>7</v>
+      </c>
+      <c r="B375" s="45">
+        <v>3</v>
+      </c>
+      <c r="C375" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D375" s="45">
+        <v>3</v>
+      </c>
+      <c r="E375" s="45">
+        <v>3</v>
+      </c>
+      <c r="F375" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="G375" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H375" s="45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A376" s="46">
+        <v>7</v>
+      </c>
+      <c r="B376" s="45">
+        <v>3</v>
+      </c>
+      <c r="C376" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D376" s="45">
+        <v>3</v>
+      </c>
+      <c r="E376" s="45">
+        <v>3</v>
+      </c>
+      <c r="F376" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="G376" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H376" s="45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A377" s="46">
+        <v>7</v>
+      </c>
+      <c r="B377" s="45">
+        <v>4</v>
+      </c>
+      <c r="C377" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D377" s="46">
+        <v>1</v>
+      </c>
+      <c r="E377" s="46">
+        <v>2</v>
+      </c>
+      <c r="F377" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G377" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H377" s="45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A378" s="46">
+        <v>7</v>
+      </c>
+      <c r="B378" s="45">
+        <v>4</v>
+      </c>
+      <c r="C378" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D378" s="46">
+        <v>1</v>
+      </c>
+      <c r="E378" s="46">
+        <v>2</v>
+      </c>
+      <c r="F378" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="G378" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H378" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A379" s="46">
+        <v>7</v>
+      </c>
+      <c r="B379" s="45">
+        <v>4</v>
+      </c>
+      <c r="C379" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D379" s="46">
+        <v>1</v>
+      </c>
+      <c r="E379" s="46">
+        <v>2</v>
+      </c>
+      <c r="F379" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="G379" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H379" s="45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A380" s="46">
+        <v>7</v>
+      </c>
+      <c r="B380" s="45">
+        <v>4</v>
+      </c>
+      <c r="C380" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D380" s="46">
+        <v>1</v>
+      </c>
+      <c r="E380" s="46">
+        <v>2</v>
+      </c>
+      <c r="F380" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="G380" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H380" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A381" s="46">
+        <v>7</v>
+      </c>
+      <c r="B381" s="45">
+        <v>4</v>
+      </c>
+      <c r="C381" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D381" s="46">
+        <v>1</v>
+      </c>
+      <c r="E381" s="46">
+        <v>2</v>
+      </c>
+      <c r="F381" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G381" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H381" s="45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A382" s="46">
+        <v>7</v>
+      </c>
+      <c r="B382" s="45">
+        <v>4</v>
+      </c>
+      <c r="C382" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D382" s="46">
+        <v>1</v>
+      </c>
+      <c r="E382" s="46">
+        <v>2</v>
+      </c>
+      <c r="F382" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="G382" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H382" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A383" s="46">
+        <v>7</v>
+      </c>
+      <c r="B383" s="45">
+        <v>4</v>
+      </c>
+      <c r="C383" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D383" s="47"/>
+      <c r="E383" s="47"/>
+      <c r="F383" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="G383" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H383" s="45" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A384" s="46">
+        <v>7</v>
+      </c>
+      <c r="B384" s="45">
+        <v>4</v>
+      </c>
+      <c r="C384" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D384" s="47"/>
+      <c r="E384" s="47"/>
+      <c r="F384" s="93" t="s">
+        <v>280</v>
+      </c>
+      <c r="G384" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H384" s="47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A385" s="46">
+        <v>7</v>
+      </c>
+      <c r="B385" s="45">
+        <v>4</v>
+      </c>
+      <c r="C385" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D385" s="47">
+        <v>2</v>
+      </c>
+      <c r="E385" s="47">
+        <v>3</v>
+      </c>
+      <c r="F385" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="G385" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H385" s="47">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A386" s="46">
+        <v>7</v>
+      </c>
+      <c r="B386" s="45">
+        <v>4</v>
+      </c>
+      <c r="C386" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D386" s="47">
+        <v>2</v>
+      </c>
+      <c r="E386" s="47">
+        <v>3</v>
+      </c>
+      <c r="F386" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="G386" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H386" s="47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A387" s="46">
+        <v>7</v>
+      </c>
+      <c r="B387" s="45">
+        <v>4</v>
+      </c>
+      <c r="C387" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D387" s="47">
+        <v>3</v>
+      </c>
+      <c r="E387" s="47">
+        <v>4</v>
+      </c>
+      <c r="F387" s="93" t="s">
+        <v>247</v>
+      </c>
+      <c r="G387" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H387" s="47" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A388" s="46">
+        <v>7</v>
+      </c>
+      <c r="B388" s="45">
+        <v>4</v>
+      </c>
+      <c r="C388" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D388" s="47">
+        <v>3</v>
+      </c>
+      <c r="E388" s="47">
+        <v>4</v>
+      </c>
+      <c r="F388" s="93" t="s">
+        <v>296</v>
+      </c>
+      <c r="G388" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H388" s="47" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A389" s="46">
+        <v>7</v>
+      </c>
+      <c r="B389" s="45">
+        <v>4</v>
+      </c>
+      <c r="C389" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D389" s="47">
+        <v>3</v>
+      </c>
+      <c r="E389" s="47">
+        <v>4</v>
+      </c>
+      <c r="F389" s="93" t="s">
+        <v>122</v>
+      </c>
+      <c r="G389" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H389" s="47">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A390" s="46">
+        <v>7</v>
+      </c>
+      <c r="B390" s="45">
+        <v>4</v>
+      </c>
+      <c r="C390" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D390" s="47">
+        <v>3</v>
+      </c>
+      <c r="E390" s="47">
+        <v>4</v>
+      </c>
+      <c r="F390" s="93" t="s">
+        <v>119</v>
+      </c>
+      <c r="G390" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H390" s="47">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C337" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C390" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>
@@ -81626,7 +88230,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:J257"/>
+  <dimension ref="A1:J286"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -88126,6 +94730,702 @@
       </c>
       <c r="I257" s="63"/>
     </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="46">
+        <v>8</v>
+      </c>
+      <c r="B258" s="46">
+        <v>1</v>
+      </c>
+      <c r="C258" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D258" s="46">
+        <v>1</v>
+      </c>
+      <c r="E258" s="46">
+        <v>2</v>
+      </c>
+      <c r="F258" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G258" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H258" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="46">
+        <v>8</v>
+      </c>
+      <c r="B259" s="46">
+        <v>1</v>
+      </c>
+      <c r="C259" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D259" s="46">
+        <v>1</v>
+      </c>
+      <c r="E259" s="46">
+        <v>2</v>
+      </c>
+      <c r="F259" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G259" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H259" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="46">
+        <v>8</v>
+      </c>
+      <c r="B260" s="46">
+        <v>1</v>
+      </c>
+      <c r="C260" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D260" s="46">
+        <v>1</v>
+      </c>
+      <c r="E260" s="46">
+        <v>2</v>
+      </c>
+      <c r="F260" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G260" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H260" s="46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="46">
+        <v>8</v>
+      </c>
+      <c r="B261" s="46">
+        <v>1</v>
+      </c>
+      <c r="C261" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D261" s="46">
+        <v>1</v>
+      </c>
+      <c r="E261" s="46">
+        <v>2</v>
+      </c>
+      <c r="F261" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G261" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H261" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="46">
+        <v>8</v>
+      </c>
+      <c r="B262" s="46">
+        <v>1</v>
+      </c>
+      <c r="C262" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D262" s="46">
+        <v>1</v>
+      </c>
+      <c r="E262" s="46">
+        <v>2</v>
+      </c>
+      <c r="F262" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G262" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="H262" s="46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="46">
+        <v>8</v>
+      </c>
+      <c r="B263" s="46">
+        <v>1</v>
+      </c>
+      <c r="C263" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D263" s="46">
+        <v>1</v>
+      </c>
+      <c r="E263" s="46">
+        <v>2</v>
+      </c>
+      <c r="F263" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G263" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H263" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="46">
+        <v>8</v>
+      </c>
+      <c r="B264" s="46">
+        <v>1</v>
+      </c>
+      <c r="C264" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D264" s="45"/>
+      <c r="E264" s="45"/>
+      <c r="F264" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="G264" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H264" s="45" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="46">
+        <v>8</v>
+      </c>
+      <c r="B265" s="46">
+        <v>1</v>
+      </c>
+      <c r="C265" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D265" s="45"/>
+      <c r="E265" s="45"/>
+      <c r="F265" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="G265" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H265" s="45" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="46">
+        <v>8</v>
+      </c>
+      <c r="B266" s="46">
+        <v>1</v>
+      </c>
+      <c r="C266" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D266" s="45"/>
+      <c r="E266" s="45"/>
+      <c r="F266" s="45" t="s">
+        <v>291</v>
+      </c>
+      <c r="G266" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H266" s="45" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="46">
+        <v>8</v>
+      </c>
+      <c r="B267" s="46">
+        <v>1</v>
+      </c>
+      <c r="C267" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D267" s="45"/>
+      <c r="E267" s="45"/>
+      <c r="F267" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="G267" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H267" s="45" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="46">
+        <v>8</v>
+      </c>
+      <c r="B268" s="46">
+        <v>1</v>
+      </c>
+      <c r="C268" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D268" s="45"/>
+      <c r="E268" s="45"/>
+      <c r="F268" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="G268" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H268" s="45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="46">
+        <v>8</v>
+      </c>
+      <c r="B269" s="46">
+        <v>1</v>
+      </c>
+      <c r="C269" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D269" s="45"/>
+      <c r="E269" s="45"/>
+      <c r="F269" s="45" t="s">
+        <v>369</v>
+      </c>
+      <c r="G269" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H269" s="45" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="46">
+        <v>8</v>
+      </c>
+      <c r="B270" s="46">
+        <v>1</v>
+      </c>
+      <c r="C270" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D270" s="45"/>
+      <c r="E270" s="45"/>
+      <c r="F270" s="45" t="s">
+        <v>370</v>
+      </c>
+      <c r="G270" s="45"/>
+      <c r="H270" s="45" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="46">
+        <v>8</v>
+      </c>
+      <c r="B271" s="46">
+        <v>1</v>
+      </c>
+      <c r="C271" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D271" s="45">
+        <v>2</v>
+      </c>
+      <c r="E271" s="45">
+        <v>3</v>
+      </c>
+      <c r="F271" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="G271" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H271" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="46">
+        <v>8</v>
+      </c>
+      <c r="B272" s="46">
+        <v>1</v>
+      </c>
+      <c r="C272" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D272" s="45">
+        <v>2</v>
+      </c>
+      <c r="E272" s="45">
+        <v>3</v>
+      </c>
+      <c r="F272" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="G272" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H272" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" s="46">
+        <v>8</v>
+      </c>
+      <c r="B273" s="46">
+        <v>1</v>
+      </c>
+      <c r="C273" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D273" s="45">
+        <v>2</v>
+      </c>
+      <c r="E273" s="45">
+        <v>3</v>
+      </c>
+      <c r="F273" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G273" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H273" s="45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" s="46">
+        <v>8</v>
+      </c>
+      <c r="B274" s="45">
+        <v>2</v>
+      </c>
+      <c r="C274" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D274" s="46">
+        <v>1</v>
+      </c>
+      <c r="E274" s="46">
+        <v>2</v>
+      </c>
+      <c r="F274" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G274" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H274" s="45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" s="46">
+        <v>8</v>
+      </c>
+      <c r="B275" s="45">
+        <v>2</v>
+      </c>
+      <c r="C275" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D275" s="46">
+        <v>1</v>
+      </c>
+      <c r="E275" s="46">
+        <v>2</v>
+      </c>
+      <c r="F275" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G275" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H275" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" s="46">
+        <v>8</v>
+      </c>
+      <c r="B276" s="45">
+        <v>2</v>
+      </c>
+      <c r="C276" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D276" s="46">
+        <v>1</v>
+      </c>
+      <c r="E276" s="46">
+        <v>2</v>
+      </c>
+      <c r="F276" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="G276" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H276" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277" s="46">
+        <v>8</v>
+      </c>
+      <c r="B277" s="45">
+        <v>2</v>
+      </c>
+      <c r="C277" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D277" s="46">
+        <v>1</v>
+      </c>
+      <c r="E277" s="46">
+        <v>2</v>
+      </c>
+      <c r="F277" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="G277" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H277" s="45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" s="46">
+        <v>8</v>
+      </c>
+      <c r="B278" s="45">
+        <v>2</v>
+      </c>
+      <c r="C278" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D278" s="46">
+        <v>1</v>
+      </c>
+      <c r="E278" s="46">
+        <v>2</v>
+      </c>
+      <c r="F278" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="G278" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H278" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" s="46">
+        <v>8</v>
+      </c>
+      <c r="B279" s="45">
+        <v>2</v>
+      </c>
+      <c r="C279" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D279" s="46">
+        <v>1</v>
+      </c>
+      <c r="E279" s="46">
+        <v>2</v>
+      </c>
+      <c r="F279" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G279" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H279" s="45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" s="46">
+        <v>8</v>
+      </c>
+      <c r="B280" s="45">
+        <v>2</v>
+      </c>
+      <c r="C280" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D280" s="45"/>
+      <c r="E280" s="45"/>
+      <c r="F280" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="G280" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H280" s="45" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" s="46">
+        <v>8</v>
+      </c>
+      <c r="B281" s="45">
+        <v>2</v>
+      </c>
+      <c r="C281" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D281" s="45"/>
+      <c r="E281" s="45"/>
+      <c r="F281" s="45" t="s">
+        <v>371</v>
+      </c>
+      <c r="G281" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H281" s="45" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" s="46">
+        <v>8</v>
+      </c>
+      <c r="B282" s="45">
+        <v>2</v>
+      </c>
+      <c r="C282" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D282" s="45"/>
+      <c r="E282" s="45"/>
+      <c r="F282" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="G282" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H282" s="45" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" s="46">
+        <v>8</v>
+      </c>
+      <c r="B283" s="45">
+        <v>2</v>
+      </c>
+      <c r="C283" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D283" s="45"/>
+      <c r="E283" s="45"/>
+      <c r="F283" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="G283" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H283" s="45" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" s="46">
+        <v>8</v>
+      </c>
+      <c r="B284" s="45">
+        <v>2</v>
+      </c>
+      <c r="C284" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D284" s="45"/>
+      <c r="E284" s="45"/>
+      <c r="F284" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="G284" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H284" s="45" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" s="46">
+        <v>8</v>
+      </c>
+      <c r="B285" s="45">
+        <v>2</v>
+      </c>
+      <c r="C285" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D285" s="45"/>
+      <c r="E285" s="45"/>
+      <c r="F285" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="G285" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H285" s="45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" s="46">
+        <v>8</v>
+      </c>
+      <c r="B286" s="45">
+        <v>2</v>
+      </c>
+      <c r="C286" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D286" s="45"/>
+      <c r="E286" s="45"/>
+      <c r="F286" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="G286" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H286" s="45" t="s">
+        <v>301</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C299" xr:uid="{00000000-0002-0000-0800-000000000000}">
